--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/ALPS_Datenbank/after_conversion_alps_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/ALPS_Datenbank/after_conversion_alps_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="452">
   <si>
     <t>location</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>Database_name</t>
   </si>
   <si>
     <t>Euganei (Euganean geothermal area - Battaglia Terme)</t>
@@ -1730,7 +1733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD312"/>
+  <dimension ref="A1:AE312"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1753,9 +1756,10 @@
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
     <col min="30" max="30" width="17.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1846,13 +1850,16 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C2">
         <v>45.28444444</v>
@@ -1873,12 +1880,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C3">
         <v>45.28694444</v>
@@ -1899,12 +1906,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C4">
         <v>45.285</v>
@@ -1925,12 +1932,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C5">
         <v>45.29583333</v>
@@ -1951,12 +1958,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C6">
         <v>44.6916766</v>
@@ -1977,12 +1984,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C7">
         <v>46.492436</v>
@@ -2024,12 +2031,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C8">
         <v>46.49255</v>
@@ -2050,12 +2057,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C9">
         <v>46.492495</v>
@@ -2097,12 +2104,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C10">
         <v>46.492144</v>
@@ -2144,12 +2151,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C11">
         <v>46.49282</v>
@@ -2170,12 +2177,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C12">
         <v>46.492916</v>
@@ -2196,12 +2203,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C13">
         <v>46.49119</v>
@@ -2222,12 +2229,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C14">
         <v>46.490844</v>
@@ -2269,12 +2276,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C15">
         <v>46.490823</v>
@@ -2316,12 +2323,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C16">
         <v>46.491967</v>
@@ -2365,10 +2372,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C17">
         <v>46.04222222</v>
@@ -2391,10 +2398,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C18">
         <v>45.7575</v>
@@ -2420,10 +2427,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C19">
         <v>46.14638889</v>
@@ -2446,10 +2453,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C20">
         <v>46.1968</v>
@@ -2505,10 +2512,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C21">
         <v>46.20346</v>
@@ -2531,10 +2538,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C22">
         <v>46.09804000000001</v>
@@ -2557,10 +2564,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C23">
         <v>46.30727</v>
@@ -2583,10 +2590,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C24">
         <v>46.23795</v>
@@ -2609,10 +2616,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C25">
         <v>46.24898</v>
@@ -2635,10 +2642,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C26">
         <v>46.19984</v>
@@ -2661,10 +2668,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C27">
         <v>46.20199</v>
@@ -2687,10 +2694,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C28">
         <v>46.26364</v>
@@ -2713,10 +2720,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C29">
         <v>46.29705</v>
@@ -2739,10 +2746,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C30">
         <v>46.31316</v>
@@ -2765,10 +2772,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C31">
         <v>46.20013</v>
@@ -2791,10 +2798,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C32">
         <v>46.24352</v>
@@ -2847,10 +2854,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C33">
         <v>45.76189</v>
@@ -2906,10 +2913,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C34">
         <v>45.85138889</v>
@@ -2932,10 +2939,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C35">
         <v>45.85138889</v>
@@ -2958,10 +2965,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C36">
         <v>45.85138889</v>
@@ -2984,10 +2991,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C37">
         <v>46.26274</v>
@@ -3040,10 +3047,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C38">
         <v>46.26274</v>
@@ -3099,10 +3106,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C39">
         <v>45.500093</v>
@@ -3125,10 +3132,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C40">
         <v>44.20638889</v>
@@ -3181,10 +3188,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C41">
         <v>44.20638889</v>
@@ -3207,10 +3214,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C42">
         <v>44.20638889</v>
@@ -3233,10 +3240,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C43">
         <v>44.20638889</v>
@@ -3289,10 +3296,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C44">
         <v>44.20638889</v>
@@ -3339,10 +3346,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C45">
         <v>44.28861111</v>
@@ -3395,10 +3402,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C46">
         <v>44.28861111</v>
@@ -3421,10 +3428,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C47">
         <v>44.28861111</v>
@@ -3471,10 +3478,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C48">
         <v>44.28861111</v>
@@ -3527,10 +3534,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C49">
         <v>44.28861111</v>
@@ -3583,10 +3590,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C50">
         <v>44.28861111</v>
@@ -3609,10 +3616,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C51">
         <v>44.28861111</v>
@@ -3635,10 +3642,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C52">
         <v>44.66305556</v>
@@ -3661,10 +3668,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B53" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C53">
         <v>44.67527778</v>
@@ -3711,10 +3718,10 @@
     </row>
     <row r="54" spans="1:30">
       <c r="A54" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B54" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C54">
         <v>44.66305556</v>
@@ -3737,10 +3744,10 @@
     </row>
     <row r="55" spans="1:30">
       <c r="A55" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B55" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C55">
         <v>44.7</v>
@@ -3793,10 +3800,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B56" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C56">
         <v>44.6333333</v>
@@ -3849,10 +3856,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B57" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C57">
         <v>44.6333333</v>
@@ -3905,10 +3912,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B58" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C58">
         <v>44.6666667</v>
@@ -3961,10 +3968,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B59" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C59">
         <v>44.5833333</v>
@@ -4017,10 +4024,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B60" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C60">
         <v>44.6833333</v>
@@ -4073,10 +4080,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B61" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C61">
         <v>44.6833333</v>
@@ -4129,10 +4136,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B62" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C62">
         <v>44.6833333</v>
@@ -4185,10 +4192,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C63">
         <v>44.3572222</v>
@@ -4238,10 +4245,10 @@
     </row>
     <row r="64" spans="1:30">
       <c r="A64" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B64" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C64">
         <v>44.7</v>
@@ -4294,10 +4301,10 @@
     </row>
     <row r="65" spans="1:30">
       <c r="A65" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B65" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C65">
         <v>44.6833333</v>
@@ -4350,10 +4357,10 @@
     </row>
     <row r="66" spans="1:30">
       <c r="A66" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B66" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C66">
         <v>46.042222</v>
@@ -4376,10 +4383,10 @@
     </row>
     <row r="67" spans="1:30">
       <c r="A67" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B67" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C67">
         <v>44.661944</v>
@@ -4402,10 +4409,10 @@
     </row>
     <row r="68" spans="1:30">
       <c r="A68" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B68" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C68">
         <v>45.368333</v>
@@ -4428,10 +4435,10 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B69" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C69">
         <v>45.276667</v>
@@ -4454,10 +4461,10 @@
     </row>
     <row r="70" spans="1:30">
       <c r="A70" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B70" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C70">
         <v>45.268889</v>
@@ -4480,10 +4487,10 @@
     </row>
     <row r="71" spans="1:30">
       <c r="A71" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B71" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C71">
         <v>45.264444</v>
@@ -4506,10 +4513,10 @@
     </row>
     <row r="72" spans="1:30">
       <c r="A72" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B72" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C72">
         <v>45.4</v>
@@ -4532,10 +4539,10 @@
     </row>
     <row r="73" spans="1:30">
       <c r="A73" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B73" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C73">
         <v>45.447222</v>
@@ -4561,10 +4568,10 @@
     </row>
     <row r="74" spans="1:30">
       <c r="A74" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B74" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C74">
         <v>45.402222</v>
@@ -4587,10 +4594,10 @@
     </row>
     <row r="75" spans="1:30">
       <c r="A75" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B75" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C75">
         <v>45.396944</v>
@@ -4613,10 +4620,10 @@
     </row>
     <row r="76" spans="1:30">
       <c r="A76" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B76" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C76">
         <v>45.408889</v>
@@ -4639,10 +4646,10 @@
     </row>
     <row r="77" spans="1:30">
       <c r="A77" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B77" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C77">
         <v>45.408889</v>
@@ -4668,10 +4675,10 @@
     </row>
     <row r="78" spans="1:30">
       <c r="A78" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B78" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C78">
         <v>45.307222</v>
@@ -4694,10 +4701,10 @@
     </row>
     <row r="79" spans="1:30">
       <c r="A79" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B79" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C79">
         <v>45.256944</v>
@@ -4720,10 +4727,10 @@
     </row>
     <row r="80" spans="1:30">
       <c r="A80" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B80" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C80">
         <v>45.408889</v>
@@ -4746,10 +4753,10 @@
     </row>
     <row r="81" spans="1:30">
       <c r="A81" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B81" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C81">
         <v>45.396667</v>
@@ -4772,7 +4779,7 @@
     </row>
     <row r="82" spans="1:30">
       <c r="A82" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C82">
         <v>45.773644</v>
@@ -4819,10 +4826,10 @@
     </row>
     <row r="83" spans="1:30">
       <c r="A83" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B83" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C83">
         <v>46.45469</v>
@@ -4875,10 +4882,10 @@
     </row>
     <row r="84" spans="1:30">
       <c r="A84" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B84" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C84">
         <v>46.45469</v>
@@ -4928,10 +4935,10 @@
     </row>
     <row r="85" spans="1:30">
       <c r="A85" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B85" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C85">
         <v>46.45469</v>
@@ -4981,10 +4988,10 @@
     </row>
     <row r="86" spans="1:30">
       <c r="A86" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B86" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C86">
         <v>46.6129</v>
@@ -5037,10 +5044,10 @@
     </row>
     <row r="87" spans="1:30">
       <c r="A87" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B87" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C87">
         <v>46.9693</v>
@@ -5096,7 +5103,7 @@
     </row>
     <row r="88" spans="1:30">
       <c r="A88" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C88">
         <v>46.61848</v>
@@ -5140,7 +5147,7 @@
     </row>
     <row r="89" spans="1:30">
       <c r="A89" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C89">
         <v>46.08115</v>
@@ -5196,10 +5203,10 @@
     </row>
     <row r="90" spans="1:30">
       <c r="A90" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B90" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C90">
         <v>46.30173</v>
@@ -5255,10 +5262,10 @@
     </row>
     <row r="91" spans="1:30">
       <c r="A91" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B91" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C91">
         <v>46.30225</v>
@@ -5314,10 +5321,10 @@
     </row>
     <row r="92" spans="1:30">
       <c r="A92" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B92" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C92">
         <v>46.18651</v>
@@ -5373,10 +5380,10 @@
     </row>
     <row r="93" spans="1:30">
       <c r="A93" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B93" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C93">
         <v>46.18736</v>
@@ -5432,10 +5439,10 @@
     </row>
     <row r="94" spans="1:30">
       <c r="A94" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B94" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C94">
         <v>46.5627</v>
@@ -5488,10 +5495,10 @@
     </row>
     <row r="95" spans="1:30">
       <c r="A95" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B95" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C95">
         <v>46.2077</v>
@@ -5538,10 +5545,10 @@
     </row>
     <row r="96" spans="1:30">
       <c r="A96" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B96" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C96">
         <v>46.38643</v>
@@ -5597,10 +5604,10 @@
     </row>
     <row r="97" spans="1:30">
       <c r="A97" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B97" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C97">
         <v>46.38173</v>
@@ -5656,10 +5663,10 @@
     </row>
     <row r="98" spans="1:30">
       <c r="A98" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B98" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C98">
         <v>46.3815</v>
@@ -5715,10 +5722,10 @@
     </row>
     <row r="99" spans="1:30">
       <c r="A99" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B99" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C99">
         <v>46.38397</v>
@@ -5774,10 +5781,10 @@
     </row>
     <row r="100" spans="1:30">
       <c r="A100" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B100" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C100">
         <v>46.37746</v>
@@ -5833,10 +5840,10 @@
     </row>
     <row r="101" spans="1:30">
       <c r="A101" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B101" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C101">
         <v>46.37881</v>
@@ -5892,10 +5899,10 @@
     </row>
     <row r="102" spans="1:30">
       <c r="A102" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B102" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C102">
         <v>46.18258</v>
@@ -5951,10 +5958,10 @@
     </row>
     <row r="103" spans="1:30">
       <c r="A103" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B103" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C103">
         <v>46.71674</v>
@@ -6007,10 +6014,10 @@
     </row>
     <row r="104" spans="1:30">
       <c r="A104" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B104" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C104">
         <v>45.7630254</v>
@@ -6063,10 +6070,10 @@
     </row>
     <row r="105" spans="1:30">
       <c r="A105" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B105" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C105">
         <v>46.7729</v>
@@ -6125,10 +6132,10 @@
     </row>
     <row r="106" spans="1:30">
       <c r="A106" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B106" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C106">
         <v>46.76984</v>
@@ -6181,10 +6188,10 @@
     </row>
     <row r="107" spans="1:30">
       <c r="A107" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B107" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C107">
         <v>46.14504</v>
@@ -6243,10 +6250,10 @@
     </row>
     <row r="108" spans="1:30">
       <c r="A108" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B108" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C108">
         <v>46.6875</v>
@@ -6299,10 +6306,10 @@
     </row>
     <row r="109" spans="1:30">
       <c r="A109" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B109" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C109">
         <v>46.20722</v>
@@ -6358,10 +6365,10 @@
     </row>
     <row r="110" spans="1:30">
       <c r="A110" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B110" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C110">
         <v>46.20722</v>
@@ -6417,10 +6424,10 @@
     </row>
     <row r="111" spans="1:30">
       <c r="A111" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B111" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C111">
         <v>46.07518</v>
@@ -6476,10 +6483,10 @@
     </row>
     <row r="112" spans="1:30">
       <c r="A112" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B112" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C112">
         <v>46.622011</v>
@@ -6535,10 +6542,10 @@
     </row>
     <row r="113" spans="1:30">
       <c r="A113" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B113" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C113">
         <v>46.1510041</v>
@@ -6594,10 +6601,10 @@
     </row>
     <row r="114" spans="1:30">
       <c r="A114" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B114" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C114">
         <v>46.07655436</v>
@@ -6653,10 +6660,10 @@
     </row>
     <row r="115" spans="1:30">
       <c r="A115" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B115" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C115">
         <v>47.00229052</v>
@@ -6679,10 +6686,10 @@
     </row>
     <row r="116" spans="1:30">
       <c r="A116" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B116" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C116">
         <v>47.36492038</v>
@@ -6705,10 +6712,10 @@
     </row>
     <row r="117" spans="1:30">
       <c r="A117" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B117" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C117">
         <v>48.008769</v>
@@ -6767,10 +6774,10 @@
     </row>
     <row r="118" spans="1:30">
       <c r="A118" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B118" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C118">
         <v>48.008769</v>
@@ -6826,10 +6833,10 @@
     </row>
     <row r="119" spans="1:30">
       <c r="A119" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B119" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C119">
         <v>48.008769</v>
@@ -6882,10 +6889,10 @@
     </row>
     <row r="120" spans="1:30">
       <c r="A120" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B120" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C120">
         <v>48.008769</v>
@@ -6938,10 +6945,10 @@
     </row>
     <row r="121" spans="1:30">
       <c r="A121" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B121" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C121">
         <v>48.008769</v>
@@ -6994,10 +7001,10 @@
     </row>
     <row r="122" spans="1:30">
       <c r="A122" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B122" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C122">
         <v>48.008769</v>
@@ -7050,10 +7057,10 @@
     </row>
     <row r="123" spans="1:30">
       <c r="A123" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B123" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C123">
         <v>48.008769</v>
@@ -7103,10 +7110,10 @@
     </row>
     <row r="124" spans="1:30">
       <c r="A124" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B124" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C124">
         <v>48.008769</v>
@@ -7159,10 +7166,10 @@
     </row>
     <row r="125" spans="1:30">
       <c r="A125" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B125" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C125">
         <v>47.772023</v>
@@ -7215,10 +7222,10 @@
     </row>
     <row r="126" spans="1:30">
       <c r="A126" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B126" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C126">
         <v>47.967323</v>
@@ -7271,10 +7278,10 @@
     </row>
     <row r="127" spans="1:30">
       <c r="A127" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B127" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C127">
         <v>47.8321</v>
@@ -7330,10 +7337,10 @@
     </row>
     <row r="128" spans="1:30">
       <c r="A128" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B128" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C128">
         <v>47.1145</v>
@@ -7374,10 +7381,10 @@
     </row>
     <row r="129" spans="1:30">
       <c r="A129" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B129" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C129">
         <v>47.1145</v>
@@ -7418,10 +7425,10 @@
     </row>
     <row r="130" spans="1:30">
       <c r="A130" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B130" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C130">
         <v>47.1145</v>
@@ -7462,10 +7469,10 @@
     </row>
     <row r="131" spans="1:30">
       <c r="A131" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B131" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C131">
         <v>47.1145</v>
@@ -7506,10 +7513,10 @@
     </row>
     <row r="132" spans="1:30">
       <c r="A132" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B132" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C132">
         <v>47.1149</v>
@@ -7553,10 +7560,10 @@
     </row>
     <row r="133" spans="1:30">
       <c r="A133" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B133" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C133">
         <v>47.1149</v>
@@ -7600,10 +7607,10 @@
     </row>
     <row r="134" spans="1:30">
       <c r="A134" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B134" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C134">
         <v>47.1149</v>
@@ -7647,10 +7654,10 @@
     </row>
     <row r="135" spans="1:30">
       <c r="A135" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B135" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C135">
         <v>47.1149</v>
@@ -7694,10 +7701,10 @@
     </row>
     <row r="136" spans="1:30">
       <c r="A136" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B136" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C136">
         <v>47.1149</v>
@@ -7741,10 +7748,10 @@
     </row>
     <row r="137" spans="1:30">
       <c r="A137" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B137" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C137">
         <v>47.1149</v>
@@ -7788,10 +7795,10 @@
     </row>
     <row r="138" spans="1:30">
       <c r="A138" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B138" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C138">
         <v>47.1149</v>
@@ -7835,10 +7842,10 @@
     </row>
     <row r="139" spans="1:30">
       <c r="A139" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B139" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C139">
         <v>47.1149</v>
@@ -7882,10 +7889,10 @@
     </row>
     <row r="140" spans="1:30">
       <c r="A140" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B140" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C140">
         <v>47.1149</v>
@@ -7941,10 +7948,10 @@
     </row>
     <row r="141" spans="1:30">
       <c r="A141" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B141" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C141">
         <v>47.1149</v>
@@ -8003,10 +8010,10 @@
     </row>
     <row r="142" spans="1:30">
       <c r="A142" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B142" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C142">
         <v>47.1149</v>
@@ -8065,10 +8072,10 @@
     </row>
     <row r="143" spans="1:30">
       <c r="A143" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B143" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C143">
         <v>46.9803</v>
@@ -8121,10 +8128,10 @@
     </row>
     <row r="144" spans="1:30">
       <c r="A144" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B144" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C144">
         <v>46.9803</v>
@@ -8177,10 +8184,10 @@
     </row>
     <row r="145" spans="1:30">
       <c r="A145" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B145" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C145">
         <v>46.5886</v>
@@ -8227,10 +8234,10 @@
     </row>
     <row r="146" spans="1:30">
       <c r="A146" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B146" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C146">
         <v>46.5886</v>
@@ -8253,10 +8260,10 @@
     </row>
     <row r="147" spans="1:30">
       <c r="A147" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B147" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C147">
         <v>46.5886</v>
@@ -8309,10 +8316,10 @@
     </row>
     <row r="148" spans="1:30">
       <c r="A148" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B148" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C148">
         <v>46.5886</v>
@@ -8335,10 +8342,10 @@
     </row>
     <row r="149" spans="1:30">
       <c r="A149" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B149" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C149">
         <v>46.5886</v>
@@ -8391,10 +8398,10 @@
     </row>
     <row r="150" spans="1:30">
       <c r="A150" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B150" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C150">
         <v>46.5886</v>
@@ -8447,10 +8454,10 @@
     </row>
     <row r="151" spans="1:30">
       <c r="A151" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B151" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C151">
         <v>46.5886</v>
@@ -8503,10 +8510,10 @@
     </row>
     <row r="152" spans="1:30">
       <c r="A152" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B152" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C152">
         <v>46.5886</v>
@@ -8559,7 +8566,7 @@
     </row>
     <row r="153" spans="1:30">
       <c r="A153" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C153">
         <v>47.1422</v>
@@ -8603,7 +8610,7 @@
     </row>
     <row r="154" spans="1:30">
       <c r="A154" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C154">
         <v>47.9261</v>
@@ -8659,7 +8666,7 @@
     </row>
     <row r="155" spans="1:30">
       <c r="A155" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C155">
         <v>47.9739</v>
@@ -8706,10 +8713,10 @@
     </row>
     <row r="156" spans="1:30">
       <c r="A156" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B156" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C156">
         <v>47.7195</v>
@@ -8732,10 +8739,10 @@
     </row>
     <row r="157" spans="1:30">
       <c r="A157" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B157" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C157">
         <v>47.743516</v>
@@ -8791,10 +8798,10 @@
     </row>
     <row r="158" spans="1:30">
       <c r="A158" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B158" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C158">
         <v>47.719742</v>
@@ -8853,10 +8860,10 @@
     </row>
     <row r="159" spans="1:30">
       <c r="A159" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B159" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C159">
         <v>47.7338</v>
@@ -8900,10 +8907,10 @@
     </row>
     <row r="160" spans="1:30">
       <c r="A160" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B160" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C160">
         <v>47.582</v>
@@ -8956,10 +8963,10 @@
     </row>
     <row r="161" spans="1:30">
       <c r="A161" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B161" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C161">
         <v>47.582</v>
@@ -9015,7 +9022,7 @@
     </row>
     <row r="162" spans="1:30">
       <c r="A162" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C162">
         <v>47.3367</v>
@@ -9065,7 +9072,7 @@
     </row>
     <row r="163" spans="1:30">
       <c r="A163" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C163">
         <v>47.3491</v>
@@ -9109,7 +9116,7 @@
     </row>
     <row r="164" spans="1:30">
       <c r="A164" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C164">
         <v>47.4213</v>
@@ -9150,7 +9157,7 @@
     </row>
     <row r="165" spans="1:30">
       <c r="A165" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C165">
         <v>47.1795</v>
@@ -9197,7 +9204,7 @@
     </row>
     <row r="166" spans="1:30">
       <c r="A166" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C166">
         <v>47.0951</v>
@@ -9238,7 +9245,7 @@
     </row>
     <row r="167" spans="1:30">
       <c r="A167" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C167">
         <v>47.5511</v>
@@ -9288,10 +9295,10 @@
     </row>
     <row r="168" spans="1:30">
       <c r="A168" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B168" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C168">
         <v>47.2091</v>
@@ -9350,10 +9357,10 @@
     </row>
     <row r="169" spans="1:30">
       <c r="A169" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B169" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C169">
         <v>47.2091</v>
@@ -9409,10 +9416,10 @@
     </row>
     <row r="170" spans="1:30">
       <c r="A170" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B170" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C170">
         <v>46.9275</v>
@@ -9453,10 +9460,10 @@
     </row>
     <row r="171" spans="1:30">
       <c r="A171" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B171" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C171">
         <v>46.9275</v>
@@ -9506,10 +9513,10 @@
     </row>
     <row r="172" spans="1:30">
       <c r="A172" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B172" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C172">
         <v>47.065</v>
@@ -9553,10 +9560,10 @@
     </row>
     <row r="173" spans="1:30">
       <c r="A173" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B173" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C173">
         <v>47.065</v>
@@ -9597,10 +9604,10 @@
     </row>
     <row r="174" spans="1:30">
       <c r="A174" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B174" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C174">
         <v>46.4869</v>
@@ -9638,7 +9645,7 @@
     </row>
     <row r="175" spans="1:30">
       <c r="A175" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C175">
         <v>46.7236</v>
@@ -9679,10 +9686,10 @@
     </row>
     <row r="176" spans="1:30">
       <c r="A176" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B176" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C176">
         <v>46.9887</v>
@@ -9732,10 +9739,10 @@
     </row>
     <row r="177" spans="1:30">
       <c r="A177" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B177" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C177">
         <v>46.9887</v>
@@ -9785,10 +9792,10 @@
     </row>
     <row r="178" spans="1:30">
       <c r="A178" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B178" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C178">
         <v>46.8892</v>
@@ -9841,7 +9848,7 @@
     </row>
     <row r="179" spans="1:30">
       <c r="A179" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C179">
         <v>46.902</v>
@@ -9882,10 +9889,10 @@
     </row>
     <row r="180" spans="1:30">
       <c r="A180" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B180" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C180">
         <v>47.0784</v>
@@ -9941,10 +9948,10 @@
     </row>
     <row r="181" spans="1:30">
       <c r="A181" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B181" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C181">
         <v>47.0761</v>
@@ -10000,7 +10007,7 @@
     </row>
     <row r="182" spans="1:30">
       <c r="A182" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C182">
         <v>47.2412</v>
@@ -10044,7 +10051,7 @@
     </row>
     <row r="183" spans="1:30">
       <c r="A183" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C183">
         <v>47.3718</v>
@@ -10085,7 +10092,7 @@
     </row>
     <row r="184" spans="1:30">
       <c r="A184" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C184">
         <v>46.6735</v>
@@ -10126,7 +10133,7 @@
     </row>
     <row r="185" spans="1:30">
       <c r="A185" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C185">
         <v>47.3681</v>
@@ -10182,10 +10189,10 @@
     </row>
     <row r="186" spans="1:30">
       <c r="A186" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B186" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C186">
         <v>47.022549</v>
@@ -10244,10 +10251,10 @@
     </row>
     <row r="187" spans="1:30">
       <c r="A187" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B187" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C187">
         <v>47.022549</v>
@@ -10300,10 +10307,10 @@
     </row>
     <row r="188" spans="1:30">
       <c r="A188" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B188" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C188">
         <v>47.022549</v>
@@ -10362,10 +10369,10 @@
     </row>
     <row r="189" spans="1:30">
       <c r="A189" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B189" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C189">
         <v>47.022549</v>
@@ -10424,10 +10431,10 @@
     </row>
     <row r="190" spans="1:30">
       <c r="A190" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B190" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C190">
         <v>47.022549</v>
@@ -10483,10 +10490,10 @@
     </row>
     <row r="191" spans="1:30">
       <c r="A191" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B191" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C191">
         <v>48.031542</v>
@@ -10512,10 +10519,10 @@
     </row>
     <row r="192" spans="1:30">
       <c r="A192" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B192" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C192">
         <v>47.66422</v>
@@ -10571,10 +10578,10 @@
     </row>
     <row r="193" spans="1:30">
       <c r="A193" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B193" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C193">
         <v>47.668206</v>
@@ -10630,10 +10637,10 @@
     </row>
     <row r="194" spans="1:30">
       <c r="A194" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B194" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C194">
         <v>47.611275</v>
@@ -10689,10 +10696,10 @@
     </row>
     <row r="195" spans="1:30">
       <c r="A195" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B195" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C195">
         <v>47.510362</v>
@@ -10751,10 +10758,10 @@
     </row>
     <row r="196" spans="1:30">
       <c r="A196" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B196" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C196">
         <v>46.816876</v>
@@ -10807,10 +10814,10 @@
     </row>
     <row r="197" spans="1:30">
       <c r="A197" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B197" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C197">
         <v>47.311421</v>
@@ -10860,10 +10867,10 @@
     </row>
     <row r="198" spans="1:30">
       <c r="A198" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B198" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C198">
         <v>47.907481</v>
@@ -10928,10 +10935,10 @@
     </row>
     <row r="199" spans="1:30">
       <c r="A199" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B199" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C199">
         <v>47.833372</v>
@@ -10984,10 +10991,10 @@
     </row>
     <row r="200" spans="1:30">
       <c r="A200" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B200" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C200">
         <v>47.619332</v>
@@ -11049,10 +11056,10 @@
     </row>
     <row r="201" spans="1:30">
       <c r="A201" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B201" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C201">
         <v>47.772905</v>
@@ -11108,10 +11115,10 @@
     </row>
     <row r="202" spans="1:30">
       <c r="A202" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B202" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C202">
         <v>47.446304</v>
@@ -11170,10 +11177,10 @@
     </row>
     <row r="203" spans="1:30">
       <c r="A203" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B203" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C203">
         <v>47.446304</v>
@@ -11235,10 +11242,10 @@
     </row>
     <row r="204" spans="1:30">
       <c r="A204" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B204" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C204">
         <v>47.332869</v>
@@ -11303,10 +11310,10 @@
     </row>
     <row r="205" spans="1:30">
       <c r="A205" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B205" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C205">
         <v>46.92752</v>
@@ -11362,10 +11369,10 @@
     </row>
     <row r="206" spans="1:30">
       <c r="A206" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B206" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C206">
         <v>46.894354</v>
@@ -11421,10 +11428,10 @@
     </row>
     <row r="207" spans="1:30">
       <c r="A207" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B207" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C207">
         <v>46.950836</v>
@@ -11474,10 +11481,10 @@
     </row>
     <row r="208" spans="1:30">
       <c r="A208" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B208" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C208">
         <v>46.96412</v>
@@ -11530,10 +11537,10 @@
     </row>
     <row r="209" spans="1:30">
       <c r="A209" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B209" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C209">
         <v>47.016095</v>
@@ -11589,10 +11596,10 @@
     </row>
     <row r="210" spans="1:30">
       <c r="A210" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B210" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C210">
         <v>46.478632</v>
@@ -11648,10 +11655,10 @@
     </row>
     <row r="211" spans="1:30">
       <c r="A211" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B211" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C211">
         <v>46.478632</v>
@@ -11707,10 +11714,10 @@
     </row>
     <row r="212" spans="1:30">
       <c r="A212" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B212" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C212">
         <v>46.475592</v>
@@ -11763,10 +11770,10 @@
     </row>
     <row r="213" spans="1:30">
       <c r="A213" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B213" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C213">
         <v>46.425898</v>
@@ -11819,10 +11826,10 @@
     </row>
     <row r="214" spans="1:30">
       <c r="A214" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B214" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C214">
         <v>46.425898</v>
@@ -11875,10 +11882,10 @@
     </row>
     <row r="215" spans="1:30">
       <c r="A215" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B215" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C215">
         <v>46.42049</v>
@@ -11934,10 +11941,10 @@
     </row>
     <row r="216" spans="1:30">
       <c r="A216" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B216" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C216">
         <v>46.42049</v>
@@ -11996,10 +12003,10 @@
     </row>
     <row r="217" spans="1:30">
       <c r="A217" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B217" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C217">
         <v>46.425654</v>
@@ -12049,10 +12056,10 @@
     </row>
     <row r="218" spans="1:30">
       <c r="A218" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B218" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C218">
         <v>46.740152</v>
@@ -12102,10 +12109,10 @@
     </row>
     <row r="219" spans="1:30">
       <c r="A219" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B219" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C219">
         <v>46.737775</v>
@@ -12164,10 +12171,10 @@
     </row>
     <row r="220" spans="1:30">
       <c r="A220" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B220" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C220">
         <v>46.667161</v>
@@ -12226,10 +12233,10 @@
     </row>
     <row r="221" spans="1:30">
       <c r="A221" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B221" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C221">
         <v>46.72917800000001</v>
@@ -12288,10 +12295,10 @@
     </row>
     <row r="222" spans="1:30">
       <c r="A222" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B222" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C222">
         <v>46.726966</v>
@@ -12350,10 +12357,10 @@
     </row>
     <row r="223" spans="1:30">
       <c r="A223" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B223" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C223">
         <v>46.722534</v>
@@ -12412,10 +12419,10 @@
     </row>
     <row r="224" spans="1:30">
       <c r="A224" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B224" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C224">
         <v>46.883205</v>
@@ -12468,10 +12475,10 @@
     </row>
     <row r="225" spans="1:30">
       <c r="A225" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B225" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C225">
         <v>46.905769</v>
@@ -12527,10 +12534,10 @@
     </row>
     <row r="226" spans="1:30">
       <c r="A226" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B226" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C226">
         <v>46.814254</v>
@@ -12586,10 +12593,10 @@
     </row>
     <row r="227" spans="1:30">
       <c r="A227" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B227" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C227">
         <v>47.987145</v>
@@ -12654,10 +12661,10 @@
     </row>
     <row r="228" spans="1:30">
       <c r="A228" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B228" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C228">
         <v>47.987145</v>
@@ -12722,10 +12729,10 @@
     </row>
     <row r="229" spans="1:30">
       <c r="A229" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B229" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C229">
         <v>47.987145</v>
@@ -12790,10 +12797,10 @@
     </row>
     <row r="230" spans="1:30">
       <c r="A230" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B230" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C230">
         <v>47.42863300000001</v>
@@ -12855,10 +12862,10 @@
     </row>
     <row r="231" spans="1:30">
       <c r="A231" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B231" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C231">
         <v>47.133327</v>
@@ -12908,10 +12915,10 @@
     </row>
     <row r="232" spans="1:30">
       <c r="A232" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B232" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C232">
         <v>47.287951</v>
@@ -12967,10 +12974,10 @@
     </row>
     <row r="233" spans="1:30">
       <c r="A233" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B233" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C233">
         <v>46.919494</v>
@@ -13020,10 +13027,10 @@
     </row>
     <row r="234" spans="1:30">
       <c r="A234" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B234" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C234">
         <v>47.473067</v>
@@ -13085,10 +13092,10 @@
     </row>
     <row r="235" spans="1:30">
       <c r="A235" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B235" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C235">
         <v>47.472165</v>
@@ -13147,10 +13154,10 @@
     </row>
     <row r="236" spans="1:30">
       <c r="A236" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B236" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C236">
         <v>47.361698</v>
@@ -13206,10 +13213,10 @@
     </row>
     <row r="237" spans="1:30">
       <c r="A237" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B237" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C237">
         <v>47.24402</v>
@@ -13268,10 +13275,10 @@
     </row>
     <row r="238" spans="1:30">
       <c r="A238" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B238" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C238">
         <v>47.182296</v>
@@ -13327,10 +13334,10 @@
     </row>
     <row r="239" spans="1:30">
       <c r="A239" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B239" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C239">
         <v>47.561781</v>
@@ -13386,10 +13393,10 @@
     </row>
     <row r="240" spans="1:30">
       <c r="A240" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B240" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C240">
         <v>47.561781</v>
@@ -13445,10 +13452,10 @@
     </row>
     <row r="241" spans="1:30">
       <c r="A241" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B241" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C241">
         <v>47.561781</v>
@@ -13507,10 +13514,10 @@
     </row>
     <row r="242" spans="1:30">
       <c r="A242" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B242" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C242">
         <v>47.561781</v>
@@ -13566,10 +13573,10 @@
     </row>
     <row r="243" spans="1:30">
       <c r="A243" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B243" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C243">
         <v>47.561781</v>
@@ -13625,10 +13632,10 @@
     </row>
     <row r="244" spans="1:30">
       <c r="A244" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B244" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C244">
         <v>47.561781</v>
@@ -13684,10 +13691,10 @@
     </row>
     <row r="245" spans="1:30">
       <c r="A245" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B245" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C245">
         <v>47.418972</v>
@@ -13749,10 +13756,10 @@
     </row>
     <row r="246" spans="1:30">
       <c r="A246" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B246" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C246">
         <v>45.99768066</v>
@@ -13775,10 +13782,10 @@
     </row>
     <row r="247" spans="1:30">
       <c r="A247" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B247" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C247">
         <v>45.46832275</v>
@@ -13801,10 +13808,10 @@
     </row>
     <row r="248" spans="1:30">
       <c r="A248" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B248" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C248">
         <v>45.24450684</v>
@@ -13827,10 +13834,10 @@
     </row>
     <row r="249" spans="1:30">
       <c r="A249" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B249" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C249">
         <v>44.97888184</v>
@@ -13853,10 +13860,10 @@
     </row>
     <row r="250" spans="1:30">
       <c r="A250" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B250" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C250">
         <v>44.90747070000001</v>
@@ -13879,10 +13886,10 @@
     </row>
     <row r="251" spans="1:30">
       <c r="A251" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B251" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C251">
         <v>44.64111328</v>
@@ -13905,10 +13912,10 @@
     </row>
     <row r="252" spans="1:30">
       <c r="A252" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B252" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C252">
         <v>44.52209473</v>
@@ -13931,10 +13938,10 @@
     </row>
     <row r="253" spans="1:30">
       <c r="A253" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B253" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C253">
         <v>44.43450928</v>
@@ -13957,10 +13964,10 @@
     </row>
     <row r="254" spans="1:30">
       <c r="A254" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B254" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C254">
         <v>43.9876709</v>
@@ -13983,10 +13990,10 @@
     </row>
     <row r="255" spans="1:30">
       <c r="A255" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B255" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C255">
         <v>43.70910645</v>
@@ -14009,10 +14016,10 @@
     </row>
     <row r="256" spans="1:30">
       <c r="A256" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B256" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C256">
         <v>45.89658</v>
@@ -14071,10 +14078,10 @@
     </row>
     <row r="257" spans="1:30">
       <c r="A257" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B257" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C257">
         <v>45.89658</v>
@@ -14130,10 +14137,10 @@
     </row>
     <row r="258" spans="1:30">
       <c r="A258" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B258" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C258">
         <v>45.89658</v>
@@ -14186,7 +14193,7 @@
     </row>
     <row r="259" spans="1:30">
       <c r="A259" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C259">
         <v>45.8966667</v>
@@ -14239,10 +14246,10 @@
     </row>
     <row r="260" spans="1:30">
       <c r="A260" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B260" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C260">
         <v>43.52673060000001</v>
@@ -14265,10 +14272,10 @@
     </row>
     <row r="261" spans="1:30">
       <c r="A261" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B261" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C261">
         <v>43.52673060000001</v>
@@ -14291,10 +14298,10 @@
     </row>
     <row r="262" spans="1:30">
       <c r="A262" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B262" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C262">
         <v>45.383419</v>
@@ -14347,10 +14354,10 @@
     </row>
     <row r="263" spans="1:30">
       <c r="A263" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B263" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C263">
         <v>46.39416705</v>
@@ -14403,10 +14410,10 @@
     </row>
     <row r="264" spans="1:30">
       <c r="A264" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B264" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C264">
         <v>46.39416705</v>
@@ -14444,10 +14451,10 @@
     </row>
     <row r="265" spans="1:30">
       <c r="A265" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B265" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C265">
         <v>44.05085725</v>
@@ -14491,10 +14498,10 @@
     </row>
     <row r="266" spans="1:30">
       <c r="A266" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B266" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C266">
         <v>44.050857</v>
@@ -14538,10 +14545,10 @@
     </row>
     <row r="267" spans="1:30">
       <c r="A267" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B267" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C267">
         <v>45.45126276</v>
@@ -14564,10 +14571,10 @@
     </row>
     <row r="268" spans="1:30">
       <c r="A268" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B268" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C268">
         <v>45.45094967</v>
@@ -14623,10 +14630,10 @@
     </row>
     <row r="269" spans="1:30">
       <c r="A269" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B269" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C269">
         <v>45.55049926</v>
@@ -14679,10 +14686,10 @@
     </row>
     <row r="270" spans="1:30">
       <c r="A270" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B270" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C270">
         <v>45.92770512</v>
@@ -14705,10 +14712,10 @@
     </row>
     <row r="271" spans="1:30">
       <c r="A271" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B271" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C271">
         <v>44.82633807</v>
@@ -14740,10 +14747,10 @@
     </row>
     <row r="272" spans="1:30">
       <c r="A272" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B272" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C272">
         <v>44.82501521</v>
@@ -14799,7 +14806,7 @@
     </row>
     <row r="273" spans="1:30">
       <c r="A273" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C273">
         <v>44.08313673</v>
@@ -14822,7 +14829,7 @@
     </row>
     <row r="274" spans="1:30">
       <c r="A274" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C274">
         <v>45.89602574</v>
@@ -14869,10 +14876,10 @@
     </row>
     <row r="275" spans="1:30">
       <c r="A275" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B275" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C275">
         <v>45.27989606</v>
@@ -14916,10 +14923,10 @@
     </row>
     <row r="276" spans="1:30">
       <c r="A276" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B276" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C276">
         <v>45.51328189</v>
@@ -14945,10 +14952,10 @@
     </row>
     <row r="277" spans="1:30">
       <c r="A277" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B277" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C277">
         <v>45.51346483</v>
@@ -15004,10 +15011,10 @@
     </row>
     <row r="278" spans="1:30">
       <c r="A278" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B278" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C278">
         <v>45.5133183</v>
@@ -15063,10 +15070,10 @@
     </row>
     <row r="279" spans="1:30">
       <c r="A279" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B279" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C279">
         <v>45.51326532</v>
@@ -15119,10 +15126,10 @@
     </row>
     <row r="280" spans="1:30">
       <c r="A280" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B280" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C280">
         <v>45.51325115</v>
@@ -15178,10 +15185,10 @@
     </row>
     <row r="281" spans="1:30">
       <c r="A281" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B281" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C281">
         <v>44.1746806</v>
@@ -15243,10 +15250,10 @@
     </row>
     <row r="282" spans="1:30">
       <c r="A282" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B282" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C282">
         <v>44.16989906</v>
@@ -15305,10 +15312,10 @@
     </row>
     <row r="283" spans="1:30">
       <c r="A283" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B283" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C283">
         <v>44.1748639</v>
@@ -15367,7 +15374,7 @@
     </row>
     <row r="284" spans="1:30">
       <c r="A284" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C284">
         <v>44.95259221</v>
@@ -15390,10 +15397,10 @@
     </row>
     <row r="285" spans="1:30">
       <c r="A285" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B285" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C285">
         <v>44.91308334</v>
@@ -15419,10 +15426,10 @@
     </row>
     <row r="286" spans="1:30">
       <c r="A286" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B286" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C286">
         <v>44.137049</v>
@@ -15445,10 +15452,10 @@
     </row>
     <row r="287" spans="1:30">
       <c r="A287" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B287" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C287">
         <v>45.47125836</v>
@@ -15501,10 +15508,10 @@
     </row>
     <row r="288" spans="1:30">
       <c r="A288" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B288" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C288">
         <v>45.4712901</v>
@@ -15557,10 +15564,10 @@
     </row>
     <row r="289" spans="1:30">
       <c r="A289" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B289" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C289">
         <v>45.46584195</v>
@@ -15583,10 +15590,10 @@
     </row>
     <row r="290" spans="1:30">
       <c r="A290" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B290" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C290">
         <v>45.14215687</v>
@@ -15645,10 +15652,10 @@
     </row>
     <row r="291" spans="1:30">
       <c r="A291" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B291" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C291">
         <v>45.895295</v>
@@ -15695,10 +15702,10 @@
     </row>
     <row r="292" spans="1:30">
       <c r="A292" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B292" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C292">
         <v>46.1592</v>
@@ -15742,7 +15749,7 @@
     </row>
     <row r="293" spans="1:30">
       <c r="A293" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C293">
         <v>46.3392</v>
@@ -15789,7 +15796,7 @@
     </row>
     <row r="294" spans="1:30">
       <c r="A294" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C294">
         <v>46.27117</v>
@@ -15833,7 +15840,7 @@
     </row>
     <row r="295" spans="1:30">
       <c r="A295" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C295">
         <v>46.307762</v>
@@ -15883,7 +15890,7 @@
     </row>
     <row r="296" spans="1:30">
       <c r="A296" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C296">
         <v>46.4044</v>
@@ -15933,7 +15940,7 @@
     </row>
     <row r="297" spans="1:30">
       <c r="A297" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C297">
         <v>46.3303</v>
@@ -15992,7 +15999,7 @@
     </row>
     <row r="298" spans="1:30">
       <c r="A298" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C298">
         <v>46.3049</v>
@@ -16048,7 +16055,7 @@
     </row>
     <row r="299" spans="1:30">
       <c r="A299" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C299">
         <v>46.3547</v>
@@ -16107,7 +16114,7 @@
     </row>
     <row r="300" spans="1:30">
       <c r="A300" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C300">
         <v>46.1553</v>
@@ -16151,7 +16158,7 @@
     </row>
     <row r="301" spans="1:30">
       <c r="A301" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C301">
         <v>46.1567</v>
@@ -16198,7 +16205,7 @@
     </row>
     <row r="302" spans="1:30">
       <c r="A302" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C302">
         <v>46.13</v>
@@ -16248,7 +16255,7 @@
     </row>
     <row r="303" spans="1:30">
       <c r="A303" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C303">
         <v>46.4391</v>
@@ -16292,7 +16299,7 @@
     </row>
     <row r="304" spans="1:30">
       <c r="A304" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C304">
         <v>46.4027</v>
@@ -16336,7 +16343,7 @@
     </row>
     <row r="305" spans="1:30">
       <c r="A305" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C305">
         <v>46.3861</v>
@@ -16380,7 +16387,7 @@
     </row>
     <row r="306" spans="1:30">
       <c r="A306" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C306">
         <v>46.4024</v>
@@ -16424,7 +16431,7 @@
     </row>
     <row r="307" spans="1:30">
       <c r="A307" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C307">
         <v>46.4065</v>
@@ -16468,7 +16475,7 @@
     </row>
     <row r="308" spans="1:30">
       <c r="A308" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C308">
         <v>46.4235</v>
@@ -16509,7 +16516,7 @@
     </row>
     <row r="309" spans="1:30">
       <c r="A309" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C309">
         <v>46.4193</v>
@@ -16553,7 +16560,7 @@
     </row>
     <row r="310" spans="1:30">
       <c r="A310" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C310">
         <v>46.3962</v>
@@ -16597,7 +16604,7 @@
     </row>
     <row r="311" spans="1:30">
       <c r="A311" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C311">
         <v>46.3114</v>
@@ -16641,10 +16648,10 @@
     </row>
     <row r="312" spans="1:30">
       <c r="A312" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B312" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C312">
         <v>47.75909424</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/ALPS_Datenbank/after_conversion_alps_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/ALPS_Datenbank/after_conversion_alps_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="460">
   <si>
     <t>location</t>
   </si>
@@ -1370,6 +1370,30 @@
   </si>
   <si>
     <t>Tüfferbad</t>
+  </si>
+  <si>
+    <t>Sand and Gravel</t>
+  </si>
+  <si>
+    <t>Gypsum</t>
+  </si>
+  <si>
+    <t>Rhyolite</t>
+  </si>
+  <si>
+    <t>Andesite</t>
+  </si>
+  <si>
+    <t>Basalt</t>
+  </si>
+  <si>
+    <t>Syenite</t>
+  </si>
+  <si>
+    <t>Breccia</t>
+  </si>
+  <si>
+    <t>Limestone</t>
   </si>
 </sst>
 </file>
@@ -1740,7 +1764,7 @@
     <col min="2" max="2" width="48.7109375" customWidth="1"/>
     <col min="3" max="4" width="19.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
     <col min="7" max="7" width="22.7109375" customWidth="1"/>
     <col min="8" max="8" width="19.7109375" customWidth="1"/>
     <col min="9" max="9" width="38.7109375" customWidth="1"/>
@@ -1867,8 +1891,8 @@
       <c r="D2">
         <v>11.77885556</v>
       </c>
-      <c r="F2">
-        <v>1</v>
+      <c r="F2" t="s">
+        <v>452</v>
       </c>
       <c r="H2">
         <v>48.9</v>
@@ -1893,8 +1917,8 @@
       <c r="D3">
         <v>11.64996667</v>
       </c>
-      <c r="F3">
-        <v>6</v>
+      <c r="F3" t="s">
+        <v>453</v>
       </c>
       <c r="H3">
         <v>34.6</v>
@@ -1919,8 +1943,8 @@
       <c r="D4">
         <v>11.6483</v>
       </c>
-      <c r="F4">
-        <v>1</v>
+      <c r="F4" t="s">
+        <v>452</v>
       </c>
       <c r="H4">
         <v>30.3</v>
@@ -1945,8 +1969,8 @@
       <c r="D5">
         <v>11.64552222</v>
       </c>
-      <c r="F5">
-        <v>7</v>
+      <c r="F5" t="s">
+        <v>454</v>
       </c>
       <c r="H5">
         <v>21.2</v>
@@ -1971,8 +1995,8 @@
       <c r="D6">
         <v>8.45300523</v>
       </c>
-      <c r="F6">
-        <v>6</v>
+      <c r="F6" t="s">
+        <v>453</v>
       </c>
       <c r="H6">
         <v>59</v>
@@ -1997,8 +2021,8 @@
       <c r="D7">
         <v>10.359474</v>
       </c>
-      <c r="F7">
-        <v>1</v>
+      <c r="F7" t="s">
+        <v>452</v>
       </c>
       <c r="H7">
         <v>37.5</v>
@@ -2044,8 +2068,8 @@
       <c r="D8">
         <v>10.35926</v>
       </c>
-      <c r="F8">
-        <v>1</v>
+      <c r="F8" t="s">
+        <v>452</v>
       </c>
       <c r="H8">
         <v>36.5</v>
@@ -2070,8 +2094,8 @@
       <c r="D9">
         <v>10.35956</v>
       </c>
-      <c r="F9">
-        <v>1</v>
+      <c r="F9" t="s">
+        <v>452</v>
       </c>
       <c r="H9">
         <v>41</v>
@@ -2117,8 +2141,8 @@
       <c r="D10">
         <v>10.358343</v>
       </c>
-      <c r="F10">
-        <v>1</v>
+      <c r="F10" t="s">
+        <v>452</v>
       </c>
       <c r="H10">
         <v>42</v>
@@ -2164,8 +2188,8 @@
       <c r="D11">
         <v>10.357372</v>
       </c>
-      <c r="F11">
-        <v>1</v>
+      <c r="F11" t="s">
+        <v>452</v>
       </c>
       <c r="H11">
         <v>36</v>
@@ -2190,8 +2214,8 @@
       <c r="D12">
         <v>10.357291</v>
       </c>
-      <c r="F12">
-        <v>1</v>
+      <c r="F12" t="s">
+        <v>452</v>
       </c>
       <c r="H12">
         <v>34.5</v>
@@ -2216,8 +2240,8 @@
       <c r="D13">
         <v>10.3643</v>
       </c>
-      <c r="F13">
-        <v>1</v>
+      <c r="F13" t="s">
+        <v>452</v>
       </c>
       <c r="H13">
         <v>18.5</v>
@@ -2242,8 +2266,8 @@
       <c r="D14">
         <v>10.359989</v>
       </c>
-      <c r="F14">
-        <v>1</v>
+      <c r="F14" t="s">
+        <v>452</v>
       </c>
       <c r="H14">
         <v>37</v>
@@ -2289,8 +2313,8 @@
       <c r="D15">
         <v>10.36117</v>
       </c>
-      <c r="F15">
-        <v>1</v>
+      <c r="F15" t="s">
+        <v>452</v>
       </c>
       <c r="H15">
         <v>18.5</v>
@@ -2336,8 +2360,8 @@
       <c r="D16">
         <v>10.360826</v>
       </c>
-      <c r="F16">
-        <v>1</v>
+      <c r="F16" t="s">
+        <v>452</v>
       </c>
       <c r="H16">
         <v>39.5</v>
@@ -2383,8 +2407,8 @@
       <c r="D17">
         <v>10.8863889</v>
       </c>
-      <c r="F17">
-        <v>6</v>
+      <c r="F17" t="s">
+        <v>453</v>
       </c>
       <c r="H17">
         <v>27</v>
@@ -2409,8 +2433,8 @@
       <c r="D18">
         <v>6.9867</v>
       </c>
-      <c r="F18">
-        <v>8</v>
+      <c r="F18" t="s">
+        <v>455</v>
       </c>
       <c r="H18">
         <v>26.5</v>
@@ -2438,8 +2462,8 @@
       <c r="D19">
         <v>8.519166667</v>
       </c>
-      <c r="F19">
-        <v>8</v>
+      <c r="F19" t="s">
+        <v>455</v>
       </c>
       <c r="H19">
         <v>27.2</v>
@@ -2464,8 +2488,8 @@
       <c r="D20">
         <v>8.541600000000001</v>
       </c>
-      <c r="F20">
-        <v>8</v>
+      <c r="F20" t="s">
+        <v>455</v>
       </c>
       <c r="H20">
         <v>25.7</v>
@@ -2523,8 +2547,8 @@
       <c r="D21">
         <v>12.02082</v>
       </c>
-      <c r="F21">
-        <v>6</v>
+      <c r="F21" t="s">
+        <v>453</v>
       </c>
       <c r="H21">
         <v>7.9</v>
@@ -2549,8 +2573,8 @@
       <c r="D22">
         <v>11.8852</v>
       </c>
-      <c r="F22">
-        <v>6</v>
+      <c r="F22" t="s">
+        <v>453</v>
       </c>
       <c r="H22">
         <v>6.4</v>
@@ -2575,8 +2599,8 @@
       <c r="D23">
         <v>12.15402</v>
       </c>
-      <c r="F23">
-        <v>6</v>
+      <c r="F23" t="s">
+        <v>453</v>
       </c>
       <c r="H23">
         <v>5.2</v>
@@ -2601,8 +2625,8 @@
       <c r="D24">
         <v>12.25903</v>
       </c>
-      <c r="F24">
-        <v>6</v>
+      <c r="F24" t="s">
+        <v>453</v>
       </c>
       <c r="H24">
         <v>7.4</v>
@@ -2627,8 +2651,8 @@
       <c r="D25">
         <v>12.21316</v>
       </c>
-      <c r="F25">
-        <v>6</v>
+      <c r="F25" t="s">
+        <v>453</v>
       </c>
       <c r="H25">
         <v>5.8</v>
@@ -2653,8 +2677,8 @@
       <c r="D26">
         <v>12.21544</v>
       </c>
-      <c r="F26">
-        <v>6</v>
+      <c r="F26" t="s">
+        <v>453</v>
       </c>
       <c r="H26">
         <v>8</v>
@@ -2679,8 +2703,8 @@
       <c r="D27">
         <v>11.9727</v>
       </c>
-      <c r="F27">
-        <v>8</v>
+      <c r="F27" t="s">
+        <v>455</v>
       </c>
       <c r="H27">
         <v>6.2</v>
@@ -2705,8 +2729,8 @@
       <c r="D28">
         <v>12.1707</v>
       </c>
-      <c r="F28">
-        <v>6</v>
+      <c r="F28" t="s">
+        <v>453</v>
       </c>
       <c r="H28">
         <v>5.5</v>
@@ -2731,8 +2755,8 @@
       <c r="D29">
         <v>12.15361</v>
       </c>
-      <c r="F29">
-        <v>6</v>
+      <c r="F29" t="s">
+        <v>453</v>
       </c>
       <c r="H29">
         <v>5</v>
@@ -2757,8 +2781,8 @@
       <c r="D30">
         <v>12.15865</v>
       </c>
-      <c r="F30">
-        <v>6</v>
+      <c r="F30" t="s">
+        <v>453</v>
       </c>
       <c r="H30">
         <v>5.8</v>
@@ -2783,8 +2807,8 @@
       <c r="D31">
         <v>11.96932</v>
       </c>
-      <c r="F31">
-        <v>8</v>
+      <c r="F31" t="s">
+        <v>455</v>
       </c>
       <c r="H31">
         <v>8.199999999999999</v>
@@ -2809,8 +2833,8 @@
       <c r="D32">
         <v>9.725339999999999</v>
       </c>
-      <c r="F32">
-        <v>9</v>
+      <c r="F32" t="s">
+        <v>456</v>
       </c>
       <c r="H32">
         <v>37.9</v>
@@ -2865,8 +2889,8 @@
       <c r="D33">
         <v>6.9689</v>
       </c>
-      <c r="F33">
-        <v>8</v>
+      <c r="F33" t="s">
+        <v>455</v>
       </c>
       <c r="H33">
         <v>22.3</v>
@@ -2924,8 +2948,8 @@
       <c r="D34">
         <v>9.662777778000001</v>
       </c>
-      <c r="F34">
-        <v>6</v>
+      <c r="F34" t="s">
+        <v>453</v>
       </c>
       <c r="H34">
         <v>27</v>
@@ -2950,8 +2974,8 @@
       <c r="D35">
         <v>9.662777778000001</v>
       </c>
-      <c r="F35">
-        <v>6</v>
+      <c r="F35" t="s">
+        <v>453</v>
       </c>
       <c r="H35">
         <v>21.7</v>
@@ -2976,8 +3000,8 @@
       <c r="D36">
         <v>9.662777778000001</v>
       </c>
-      <c r="F36">
-        <v>6</v>
+      <c r="F36" t="s">
+        <v>453</v>
       </c>
       <c r="H36">
         <v>18.5</v>
@@ -3005,8 +3029,8 @@
       <c r="E37">
         <v>1650</v>
       </c>
-      <c r="F37">
-        <v>8</v>
+      <c r="F37" t="s">
+        <v>455</v>
       </c>
       <c r="H37">
         <v>29.2</v>
@@ -3061,8 +3085,8 @@
       <c r="E38">
         <v>1650</v>
       </c>
-      <c r="F38">
-        <v>8</v>
+      <c r="F38" t="s">
+        <v>455</v>
       </c>
       <c r="H38">
         <v>38.6</v>
@@ -3117,8 +3141,8 @@
       <c r="D39">
         <v>10.609565</v>
       </c>
-      <c r="F39">
-        <v>11</v>
+      <c r="F39" t="s">
+        <v>457</v>
       </c>
       <c r="H39">
         <v>69.90000000000001</v>
@@ -3143,8 +3167,8 @@
       <c r="D40">
         <v>7.269966667</v>
       </c>
-      <c r="F40">
-        <v>8</v>
+      <c r="F40" t="s">
+        <v>455</v>
       </c>
       <c r="H40">
         <v>63</v>
@@ -3199,8 +3223,8 @@
       <c r="D41">
         <v>7.269966667</v>
       </c>
-      <c r="F41">
-        <v>8</v>
+      <c r="F41" t="s">
+        <v>455</v>
       </c>
       <c r="H41">
         <v>46.8</v>
@@ -3225,8 +3249,8 @@
       <c r="D42">
         <v>7.269966667</v>
       </c>
-      <c r="F42">
-        <v>8</v>
+      <c r="F42" t="s">
+        <v>455</v>
       </c>
       <c r="H42">
         <v>60.4</v>
@@ -3251,8 +3275,8 @@
       <c r="D43">
         <v>7.269966667</v>
       </c>
-      <c r="F43">
-        <v>8</v>
+      <c r="F43" t="s">
+        <v>455</v>
       </c>
       <c r="H43">
         <v>55.4</v>
@@ -3307,8 +3331,8 @@
       <c r="D44">
         <v>7.268888888999999</v>
       </c>
-      <c r="F44">
-        <v>8</v>
+      <c r="F44" t="s">
+        <v>455</v>
       </c>
       <c r="H44">
         <v>48.8</v>
@@ -3357,8 +3381,8 @@
       <c r="D45">
         <v>7.077744444</v>
       </c>
-      <c r="F45">
-        <v>8</v>
+      <c r="F45" t="s">
+        <v>455</v>
       </c>
       <c r="H45">
         <v>46.7</v>
@@ -3413,8 +3437,8 @@
       <c r="D46">
         <v>7.076666667</v>
       </c>
-      <c r="F46">
-        <v>8</v>
+      <c r="F46" t="s">
+        <v>455</v>
       </c>
       <c r="H46">
         <v>49.5</v>
@@ -3439,8 +3463,8 @@
       <c r="D47">
         <v>7.077744444</v>
       </c>
-      <c r="F47">
-        <v>8</v>
+      <c r="F47" t="s">
+        <v>455</v>
       </c>
       <c r="H47">
         <v>50.5</v>
@@ -3489,8 +3513,8 @@
       <c r="D48">
         <v>7.077744444</v>
       </c>
-      <c r="F48">
-        <v>8</v>
+      <c r="F48" t="s">
+        <v>455</v>
       </c>
       <c r="H48">
         <v>55.2</v>
@@ -3545,8 +3569,8 @@
       <c r="D49">
         <v>7.077744444</v>
       </c>
-      <c r="F49">
-        <v>8</v>
+      <c r="F49" t="s">
+        <v>455</v>
       </c>
       <c r="H49">
         <v>55.6</v>
@@ -3601,8 +3625,8 @@
       <c r="D50">
         <v>7.077744444</v>
       </c>
-      <c r="F50">
-        <v>8</v>
+      <c r="F50" t="s">
+        <v>455</v>
       </c>
       <c r="H50">
         <v>61.2</v>
@@ -3627,8 +3651,8 @@
       <c r="D51">
         <v>7.077744444</v>
       </c>
-      <c r="F51">
-        <v>8</v>
+      <c r="F51" t="s">
+        <v>455</v>
       </c>
       <c r="H51">
         <v>58</v>
@@ -3653,8 +3677,8 @@
       <c r="D52">
         <v>8.4733</v>
       </c>
-      <c r="F52">
-        <v>6</v>
+      <c r="F52" t="s">
+        <v>453</v>
       </c>
       <c r="H52">
         <v>38.2</v>
@@ -3679,8 +3703,8 @@
       <c r="D53">
         <v>8.480555556000001</v>
       </c>
-      <c r="F53">
-        <v>1</v>
+      <c r="F53" t="s">
+        <v>452</v>
       </c>
       <c r="H53">
         <v>70.5</v>
@@ -3729,8 +3753,8 @@
       <c r="D54">
         <v>8.4733</v>
       </c>
-      <c r="F54">
-        <v>6</v>
+      <c r="F54" t="s">
+        <v>453</v>
       </c>
       <c r="H54">
         <v>56</v>
@@ -3755,8 +3779,8 @@
       <c r="D55">
         <v>8.466666667</v>
       </c>
-      <c r="F55">
-        <v>6</v>
+      <c r="F55" t="s">
+        <v>453</v>
       </c>
       <c r="H55">
         <v>69.5</v>
@@ -3811,8 +3835,8 @@
       <c r="D56">
         <v>8.466666667</v>
       </c>
-      <c r="F56">
-        <v>6</v>
+      <c r="F56" t="s">
+        <v>453</v>
       </c>
       <c r="H56">
         <v>17.4</v>
@@ -3867,8 +3891,8 @@
       <c r="D57">
         <v>8.466666667</v>
       </c>
-      <c r="F57">
-        <v>6</v>
+      <c r="F57" t="s">
+        <v>453</v>
       </c>
       <c r="H57">
         <v>18.7</v>
@@ -3923,8 +3947,8 @@
       <c r="D58">
         <v>8.483333332999999</v>
       </c>
-      <c r="F58">
-        <v>6</v>
+      <c r="F58" t="s">
+        <v>453</v>
       </c>
       <c r="H58">
         <v>30.1</v>
@@ -3979,8 +4003,8 @@
       <c r="D59">
         <v>8.449999999999999</v>
       </c>
-      <c r="F59">
-        <v>6</v>
+      <c r="F59" t="s">
+        <v>453</v>
       </c>
       <c r="H59">
         <v>13.7</v>
@@ -4035,8 +4059,8 @@
       <c r="D60">
         <v>8.5</v>
       </c>
-      <c r="F60">
-        <v>1</v>
+      <c r="F60" t="s">
+        <v>452</v>
       </c>
       <c r="H60">
         <v>37.9</v>
@@ -4091,8 +4115,8 @@
       <c r="D61">
         <v>8.5</v>
       </c>
-      <c r="F61">
-        <v>1</v>
+      <c r="F61" t="s">
+        <v>452</v>
       </c>
       <c r="H61">
         <v>32</v>
@@ -4147,8 +4171,8 @@
       <c r="D62">
         <v>8.5</v>
       </c>
-      <c r="F62">
-        <v>1</v>
+      <c r="F62" t="s">
+        <v>452</v>
       </c>
       <c r="H62">
         <v>23</v>
@@ -4203,8 +4227,8 @@
       <c r="D63">
         <v>8.445277777999999</v>
       </c>
-      <c r="F63">
-        <v>4</v>
+      <c r="F63" t="s">
+        <v>458</v>
       </c>
       <c r="H63">
         <v>14.5</v>
@@ -4256,8 +4280,8 @@
       <c r="D64">
         <v>8.466666667</v>
       </c>
-      <c r="F64">
-        <v>6</v>
+      <c r="F64" t="s">
+        <v>453</v>
       </c>
       <c r="H64">
         <v>69.5</v>
@@ -4312,8 +4336,8 @@
       <c r="D65">
         <v>8.5</v>
       </c>
-      <c r="F65">
-        <v>1</v>
+      <c r="F65" t="s">
+        <v>452</v>
       </c>
       <c r="H65">
         <v>31.5</v>
@@ -4368,8 +4392,8 @@
       <c r="D66">
         <v>10.886389</v>
       </c>
-      <c r="F66">
-        <v>6</v>
+      <c r="F66" t="s">
+        <v>453</v>
       </c>
       <c r="H66">
         <v>27</v>
@@ -4394,8 +4418,8 @@
       <c r="D67">
         <v>8.654688900000002</v>
       </c>
-      <c r="F67">
-        <v>1</v>
+      <c r="F67" t="s">
+        <v>452</v>
       </c>
       <c r="H67">
         <v>22.5</v>
@@ -4420,8 +4444,8 @@
       <c r="D68">
         <v>11.607467</v>
       </c>
-      <c r="F68">
-        <v>1</v>
+      <c r="F68" t="s">
+        <v>452</v>
       </c>
       <c r="H68">
         <v>24</v>
@@ -4446,8 +4470,8 @@
       <c r="D69">
         <v>11.742467</v>
       </c>
-      <c r="F69">
-        <v>1</v>
+      <c r="F69" t="s">
+        <v>452</v>
       </c>
       <c r="H69">
         <v>28.3</v>
@@ -4472,8 +4496,8 @@
       <c r="D70">
         <v>11.744411</v>
       </c>
-      <c r="F70">
-        <v>1</v>
+      <c r="F70" t="s">
+        <v>452</v>
       </c>
       <c r="H70">
         <v>43.1</v>
@@ -4498,8 +4522,8 @@
       <c r="D71">
         <v>11.645244</v>
       </c>
-      <c r="F71">
-        <v>1</v>
+      <c r="F71" t="s">
+        <v>452</v>
       </c>
       <c r="H71">
         <v>36</v>
@@ -4524,8 +4548,8 @@
       <c r="D72">
         <v>11.556356</v>
       </c>
-      <c r="F72">
-        <v>1</v>
+      <c r="F72" t="s">
+        <v>452</v>
       </c>
       <c r="H72">
         <v>28.5</v>
@@ -4553,8 +4577,8 @@
       <c r="E73">
         <v>54</v>
       </c>
-      <c r="F73">
-        <v>6</v>
+      <c r="F73" t="s">
+        <v>453</v>
       </c>
       <c r="H73">
         <v>26.5</v>
@@ -4579,8 +4603,8 @@
       <c r="D74">
         <v>11.569967</v>
       </c>
-      <c r="F74">
-        <v>1</v>
+      <c r="F74" t="s">
+        <v>452</v>
       </c>
       <c r="H74">
         <v>25.2</v>
@@ -4605,8 +4629,8 @@
       <c r="D75">
         <v>11.596633</v>
       </c>
-      <c r="F75">
-        <v>1</v>
+      <c r="F75" t="s">
+        <v>452</v>
       </c>
       <c r="H75">
         <v>24.6</v>
@@ -4631,8 +4655,8 @@
       <c r="D76">
         <v>11.194967</v>
       </c>
-      <c r="F76">
-        <v>1</v>
+      <c r="F76" t="s">
+        <v>452</v>
       </c>
       <c r="H76">
         <v>26.9</v>
@@ -4660,8 +4684,8 @@
       <c r="E77">
         <v>100</v>
       </c>
-      <c r="F77">
-        <v>1</v>
+      <c r="F77" t="s">
+        <v>452</v>
       </c>
       <c r="H77">
         <v>26.4</v>
@@ -4686,8 +4710,8 @@
       <c r="D78">
         <v>11.758889</v>
       </c>
-      <c r="F78">
-        <v>7</v>
+      <c r="F78" t="s">
+        <v>454</v>
       </c>
       <c r="H78">
         <v>49</v>
@@ -4712,8 +4736,8 @@
       <c r="D79">
         <v>11.748889</v>
       </c>
-      <c r="F79">
-        <v>1</v>
+      <c r="F79" t="s">
+        <v>452</v>
       </c>
       <c r="H79">
         <v>32.2</v>
@@ -4738,8 +4762,8 @@
       <c r="D80">
         <v>11.586389</v>
       </c>
-      <c r="F80">
-        <v>1</v>
+      <c r="F80" t="s">
+        <v>452</v>
       </c>
       <c r="H80">
         <v>25.8</v>
@@ -4764,8 +4788,8 @@
       <c r="D81">
         <v>11.556944</v>
       </c>
-      <c r="F81">
-        <v>1</v>
+      <c r="F81" t="s">
+        <v>452</v>
       </c>
       <c r="H81">
         <v>28.8</v>
@@ -4787,8 +4811,8 @@
       <c r="D82">
         <v>7.827468</v>
       </c>
-      <c r="F82">
-        <v>8</v>
+      <c r="F82" t="s">
+        <v>455</v>
       </c>
       <c r="H82">
         <v>42</v>
@@ -4837,8 +4861,8 @@
       <c r="D83">
         <v>8.94303</v>
       </c>
-      <c r="F83">
-        <v>1</v>
+      <c r="F83" t="s">
+        <v>452</v>
       </c>
       <c r="H83">
         <v>24.9</v>
@@ -4893,8 +4917,8 @@
       <c r="D84">
         <v>8.94303</v>
       </c>
-      <c r="F84">
-        <v>1</v>
+      <c r="F84" t="s">
+        <v>452</v>
       </c>
       <c r="H84">
         <v>24.5</v>
@@ -4946,8 +4970,8 @@
       <c r="D85">
         <v>8.94303</v>
       </c>
-      <c r="F85">
-        <v>1</v>
+      <c r="F85" t="s">
+        <v>452</v>
       </c>
       <c r="H85">
         <v>24.2</v>
@@ -4999,8 +5023,8 @@
       <c r="D86">
         <v>9.44491</v>
       </c>
-      <c r="F86">
-        <v>6</v>
+      <c r="F86" t="s">
+        <v>453</v>
       </c>
       <c r="H86">
         <v>18</v>
@@ -5055,8 +5079,8 @@
       <c r="D87">
         <v>9.48696</v>
       </c>
-      <c r="F87">
-        <v>5</v>
+      <c r="F87" t="s">
+        <v>459</v>
       </c>
       <c r="H87">
         <v>36.5</v>
@@ -5111,8 +5135,8 @@
       <c r="D88">
         <v>9.65865</v>
       </c>
-      <c r="F88">
-        <v>6</v>
+      <c r="F88" t="s">
+        <v>453</v>
       </c>
       <c r="H88">
         <v>17</v>
@@ -5155,8 +5179,8 @@
       <c r="D89">
         <v>7.098660000000002</v>
       </c>
-      <c r="F89">
-        <v>9</v>
+      <c r="F89" t="s">
+        <v>456</v>
       </c>
       <c r="H89">
         <v>21.1</v>
@@ -5214,8 +5238,8 @@
       <c r="D90">
         <v>7.92536</v>
       </c>
-      <c r="F90">
-        <v>8</v>
+      <c r="F90" t="s">
+        <v>455</v>
       </c>
       <c r="H90">
         <v>16.1</v>
@@ -5273,8 +5297,8 @@
       <c r="D91">
         <v>7.92939</v>
       </c>
-      <c r="F91">
-        <v>8</v>
+      <c r="F91" t="s">
+        <v>455</v>
       </c>
       <c r="H91">
         <v>22.5</v>
@@ -5332,8 +5356,8 @@
       <c r="D92">
         <v>7.41623</v>
       </c>
-      <c r="F92">
-        <v>3</v>
+      <c r="F92" t="s">
+        <v>454</v>
       </c>
       <c r="H92">
         <v>28</v>
@@ -5391,8 +5415,8 @@
       <c r="D93">
         <v>7.41597</v>
       </c>
-      <c r="F93">
-        <v>3</v>
+      <c r="F93" t="s">
+        <v>454</v>
       </c>
       <c r="H93">
         <v>24.9</v>
@@ -5450,8 +5474,8 @@
       <c r="D94">
         <v>8.36098</v>
       </c>
-      <c r="F94">
-        <v>8</v>
+      <c r="F94" t="s">
+        <v>455</v>
       </c>
       <c r="H94">
         <v>18.6</v>
@@ -5506,8 +5530,8 @@
       <c r="D95">
         <v>7.011839999999999</v>
       </c>
-      <c r="F95">
-        <v>1</v>
+      <c r="F95" t="s">
+        <v>452</v>
       </c>
       <c r="H95">
         <v>55</v>
@@ -5556,8 +5580,8 @@
       <c r="D96">
         <v>7.64338</v>
       </c>
-      <c r="F96">
-        <v>6</v>
+      <c r="F96" t="s">
+        <v>453</v>
       </c>
       <c r="H96">
         <v>45.5</v>
@@ -5615,8 +5639,8 @@
       <c r="D97">
         <v>7.632639999999999</v>
       </c>
-      <c r="F97">
-        <v>1</v>
+      <c r="F97" t="s">
+        <v>452</v>
       </c>
       <c r="H97">
         <v>45.9</v>
@@ -5674,8 +5698,8 @@
       <c r="D98">
         <v>7.63134</v>
       </c>
-      <c r="F98">
-        <v>1</v>
+      <c r="F98" t="s">
+        <v>452</v>
       </c>
       <c r="H98">
         <v>37.3</v>
@@ -5733,8 +5757,8 @@
       <c r="D99">
         <v>7.6346</v>
       </c>
-      <c r="F99">
-        <v>1</v>
+      <c r="F99" t="s">
+        <v>452</v>
       </c>
       <c r="H99">
         <v>43.6</v>
@@ -5792,8 +5816,8 @@
       <c r="D100">
         <v>7.62547</v>
       </c>
-      <c r="F100">
-        <v>1</v>
+      <c r="F100" t="s">
+        <v>452</v>
       </c>
       <c r="H100">
         <v>44</v>
@@ -5851,8 +5875,8 @@
       <c r="D101">
         <v>7.63003</v>
       </c>
-      <c r="F101">
-        <v>1</v>
+      <c r="F101" t="s">
+        <v>452</v>
       </c>
       <c r="H101">
         <v>51</v>
@@ -5910,8 +5934,8 @@
       <c r="D102">
         <v>7.187</v>
       </c>
-      <c r="F102">
-        <v>6</v>
+      <c r="F102" t="s">
+        <v>453</v>
       </c>
       <c r="H102">
         <v>24.2</v>
@@ -5972,8 +5996,8 @@
       <c r="E103">
         <v>8</v>
       </c>
-      <c r="F103">
-        <v>5</v>
+      <c r="F103" t="s">
+        <v>459</v>
       </c>
       <c r="H103">
         <v>15.2</v>
@@ -6025,8 +6049,8 @@
       <c r="D104">
         <v>6.985010000000001</v>
       </c>
-      <c r="F104">
-        <v>8</v>
+      <c r="F104" t="s">
+        <v>455</v>
       </c>
       <c r="H104">
         <v>36</v>
@@ -6084,8 +6108,8 @@
       <c r="E105">
         <v>8.4</v>
       </c>
-      <c r="F105">
-        <v>6</v>
+      <c r="F105" t="s">
+        <v>453</v>
       </c>
       <c r="H105">
         <v>14.7</v>
@@ -6143,8 +6167,8 @@
       <c r="D106">
         <v>9.42666</v>
       </c>
-      <c r="F106">
-        <v>1</v>
+      <c r="F106" t="s">
+        <v>452</v>
       </c>
       <c r="H106">
         <v>17.2</v>
@@ -6202,8 +6226,8 @@
       <c r="E107">
         <v>7</v>
       </c>
-      <c r="F107">
-        <v>6</v>
+      <c r="F107" t="s">
+        <v>453</v>
       </c>
       <c r="H107">
         <v>25</v>
@@ -6261,8 +6285,8 @@
       <c r="D108">
         <v>8.959</v>
       </c>
-      <c r="F108">
-        <v>8</v>
+      <c r="F108" t="s">
+        <v>455</v>
       </c>
       <c r="H108">
         <v>13.5</v>
@@ -6317,8 +6341,8 @@
       <c r="D109">
         <v>6.900930000000002</v>
       </c>
-      <c r="F109">
-        <v>5</v>
+      <c r="F109" t="s">
+        <v>459</v>
       </c>
       <c r="H109">
         <v>29.5</v>
@@ -6376,8 +6400,8 @@
       <c r="D110">
         <v>6.900930000000002</v>
       </c>
-      <c r="F110">
-        <v>5</v>
+      <c r="F110" t="s">
+        <v>459</v>
       </c>
       <c r="H110">
         <v>23.1</v>
@@ -6435,8 +6459,8 @@
       <c r="D111">
         <v>7.235580000000001</v>
       </c>
-      <c r="F111">
-        <v>3</v>
+      <c r="F111" t="s">
+        <v>454</v>
       </c>
       <c r="H111">
         <v>17.4</v>
@@ -6497,8 +6521,8 @@
       <c r="E112">
         <v>47</v>
       </c>
-      <c r="F112">
-        <v>1</v>
+      <c r="F112" t="s">
+        <v>452</v>
       </c>
       <c r="H112">
         <v>24.9</v>
@@ -6553,8 +6577,8 @@
       <c r="D113">
         <v>8.991515</v>
       </c>
-      <c r="F113">
-        <v>8</v>
+      <c r="F113" t="s">
+        <v>455</v>
       </c>
       <c r="H113">
         <v>9.6</v>
@@ -6612,8 +6636,8 @@
       <c r="D114">
         <v>8.958349999999999</v>
       </c>
-      <c r="F114">
-        <v>8</v>
+      <c r="F114" t="s">
+        <v>455</v>
       </c>
       <c r="H114">
         <v>8.4</v>
@@ -6671,8 +6695,8 @@
       <c r="D115">
         <v>11.46095773</v>
       </c>
-      <c r="F115">
-        <v>8</v>
+      <c r="F115" t="s">
+        <v>455</v>
       </c>
       <c r="H115">
         <v>21.6</v>
@@ -6697,8 +6721,8 @@
       <c r="D116">
         <v>12.16622997</v>
       </c>
-      <c r="F116">
-        <v>8</v>
+      <c r="F116" t="s">
+        <v>455</v>
       </c>
       <c r="H116">
         <v>38.8</v>
@@ -6723,8 +6747,8 @@
       <c r="D117">
         <v>16.229269</v>
       </c>
-      <c r="F117">
-        <v>5</v>
+      <c r="F117" t="s">
+        <v>459</v>
       </c>
       <c r="H117">
         <v>30.9</v>
@@ -6785,8 +6809,8 @@
       <c r="D118">
         <v>16.229269</v>
       </c>
-      <c r="F118">
-        <v>5</v>
+      <c r="F118" t="s">
+        <v>459</v>
       </c>
       <c r="H118">
         <v>31.5</v>
@@ -6844,8 +6868,8 @@
       <c r="D119">
         <v>16.229269</v>
       </c>
-      <c r="F119">
-        <v>5</v>
+      <c r="F119" t="s">
+        <v>459</v>
       </c>
       <c r="H119">
         <v>24.8</v>
@@ -6900,8 +6924,8 @@
       <c r="D120">
         <v>16.229269</v>
       </c>
-      <c r="F120">
-        <v>5</v>
+      <c r="F120" t="s">
+        <v>459</v>
       </c>
       <c r="H120">
         <v>29</v>
@@ -6956,8 +6980,8 @@
       <c r="D121">
         <v>16.229269</v>
       </c>
-      <c r="F121">
-        <v>5</v>
+      <c r="F121" t="s">
+        <v>459</v>
       </c>
       <c r="H121">
         <v>34.8</v>
@@ -7012,8 +7036,8 @@
       <c r="D122">
         <v>16.229269</v>
       </c>
-      <c r="F122">
-        <v>5</v>
+      <c r="F122" t="s">
+        <v>459</v>
       </c>
       <c r="H122">
         <v>34.6</v>
@@ -7068,8 +7092,8 @@
       <c r="D123">
         <v>16.229269</v>
       </c>
-      <c r="F123">
-        <v>5</v>
+      <c r="F123" t="s">
+        <v>459</v>
       </c>
       <c r="H123">
         <v>33.8</v>
@@ -7121,8 +7145,8 @@
       <c r="D124">
         <v>16.229269</v>
       </c>
-      <c r="F124">
-        <v>5</v>
+      <c r="F124" t="s">
+        <v>459</v>
       </c>
       <c r="H124">
         <v>32.1</v>
@@ -7177,8 +7201,8 @@
       <c r="D125">
         <v>16.323575</v>
       </c>
-      <c r="F125">
-        <v>5</v>
+      <c r="F125" t="s">
+        <v>459</v>
       </c>
       <c r="H125">
         <v>37.3</v>
@@ -7233,8 +7257,8 @@
       <c r="D126">
         <v>16.2128</v>
       </c>
-      <c r="F126">
-        <v>5</v>
+      <c r="F126" t="s">
+        <v>459</v>
       </c>
       <c r="H126">
         <v>22.1</v>
@@ -7289,8 +7313,8 @@
       <c r="D127">
         <v>16.1647</v>
       </c>
-      <c r="F127">
-        <v>5</v>
+      <c r="F127" t="s">
+        <v>459</v>
       </c>
       <c r="H127">
         <v>16.3</v>
@@ -7348,8 +7372,8 @@
       <c r="D128">
         <v>11.6831</v>
       </c>
-      <c r="F128">
-        <v>6</v>
+      <c r="F128" t="s">
+        <v>453</v>
       </c>
       <c r="H128">
         <v>18.1</v>
@@ -7392,8 +7416,8 @@
       <c r="D129">
         <v>11.6831</v>
       </c>
-      <c r="F129">
-        <v>6</v>
+      <c r="F129" t="s">
+        <v>453</v>
       </c>
       <c r="H129">
         <v>20.2</v>
@@ -7436,8 +7460,8 @@
       <c r="D130">
         <v>11.6831</v>
       </c>
-      <c r="F130">
-        <v>6</v>
+      <c r="F130" t="s">
+        <v>453</v>
       </c>
       <c r="H130">
         <v>21.5</v>
@@ -7480,8 +7504,8 @@
       <c r="D131">
         <v>11.6831</v>
       </c>
-      <c r="F131">
-        <v>6</v>
+      <c r="F131" t="s">
+        <v>453</v>
       </c>
       <c r="H131">
         <v>22.1</v>
@@ -7524,8 +7548,8 @@
       <c r="D132">
         <v>13.1365</v>
       </c>
-      <c r="F132">
-        <v>9</v>
+      <c r="F132" t="s">
+        <v>456</v>
       </c>
       <c r="H132">
         <v>36.3</v>
@@ -7571,8 +7595,8 @@
       <c r="D133">
         <v>13.1365</v>
       </c>
-      <c r="F133">
-        <v>9</v>
+      <c r="F133" t="s">
+        <v>456</v>
       </c>
       <c r="H133">
         <v>42.4</v>
@@ -7618,8 +7642,8 @@
       <c r="D134">
         <v>13.1365</v>
       </c>
-      <c r="F134">
-        <v>9</v>
+      <c r="F134" t="s">
+        <v>456</v>
       </c>
       <c r="H134">
         <v>38.1</v>
@@ -7665,8 +7689,8 @@
       <c r="D135">
         <v>13.1365</v>
       </c>
-      <c r="F135">
-        <v>9</v>
+      <c r="F135" t="s">
+        <v>456</v>
       </c>
       <c r="H135">
         <v>36.8</v>
@@ -7712,8 +7736,8 @@
       <c r="D136">
         <v>13.1365</v>
       </c>
-      <c r="F136">
-        <v>9</v>
+      <c r="F136" t="s">
+        <v>456</v>
       </c>
       <c r="H136">
         <v>38.1</v>
@@ -7759,8 +7783,8 @@
       <c r="D137">
         <v>13.1365</v>
       </c>
-      <c r="F137">
-        <v>9</v>
+      <c r="F137" t="s">
+        <v>456</v>
       </c>
       <c r="H137">
         <v>37</v>
@@ -7806,8 +7830,8 @@
       <c r="D138">
         <v>13.1365</v>
       </c>
-      <c r="F138">
-        <v>9</v>
+      <c r="F138" t="s">
+        <v>456</v>
       </c>
       <c r="H138">
         <v>23</v>
@@ -7853,8 +7877,8 @@
       <c r="D139">
         <v>13.1365</v>
       </c>
-      <c r="F139">
-        <v>9</v>
+      <c r="F139" t="s">
+        <v>456</v>
       </c>
       <c r="H139">
         <v>16.1</v>
@@ -7900,8 +7924,8 @@
       <c r="D140">
         <v>13.1365</v>
       </c>
-      <c r="F140">
-        <v>9</v>
+      <c r="F140" t="s">
+        <v>456</v>
       </c>
       <c r="H140">
         <v>45</v>
@@ -7959,8 +7983,8 @@
       <c r="D141">
         <v>13.1365</v>
       </c>
-      <c r="F141">
-        <v>9</v>
+      <c r="F141" t="s">
+        <v>456</v>
       </c>
       <c r="H141">
         <v>44</v>
@@ -8021,8 +8045,8 @@
       <c r="D142">
         <v>13.1365</v>
       </c>
-      <c r="F142">
-        <v>9</v>
+      <c r="F142" t="s">
+        <v>456</v>
       </c>
       <c r="H142">
         <v>47</v>
@@ -8083,8 +8107,8 @@
       <c r="D143">
         <v>15.3653</v>
       </c>
-      <c r="F143">
-        <v>5</v>
+      <c r="F143" t="s">
+        <v>459</v>
       </c>
       <c r="H143">
         <v>27.2</v>
@@ -8139,8 +8163,8 @@
       <c r="D144">
         <v>15.3653</v>
       </c>
-      <c r="F144">
-        <v>5</v>
+      <c r="F144" t="s">
+        <v>459</v>
       </c>
       <c r="H144">
         <v>24.1</v>
@@ -8195,8 +8219,8 @@
       <c r="D145">
         <v>13.826</v>
       </c>
-      <c r="F145">
-        <v>6</v>
+      <c r="F145" t="s">
+        <v>453</v>
       </c>
       <c r="H145">
         <v>31</v>
@@ -8245,8 +8269,8 @@
       <c r="D146">
         <v>13.826</v>
       </c>
-      <c r="F146">
-        <v>6</v>
+      <c r="F146" t="s">
+        <v>453</v>
       </c>
       <c r="H146">
         <v>28</v>
@@ -8271,8 +8295,8 @@
       <c r="D147">
         <v>13.826</v>
       </c>
-      <c r="F147">
-        <v>6</v>
+      <c r="F147" t="s">
+        <v>453</v>
       </c>
       <c r="H147">
         <v>28.5</v>
@@ -8327,8 +8351,8 @@
       <c r="D148">
         <v>13.826</v>
       </c>
-      <c r="F148">
-        <v>6</v>
+      <c r="F148" t="s">
+        <v>453</v>
       </c>
       <c r="H148">
         <v>28.5</v>
@@ -8353,8 +8377,8 @@
       <c r="D149">
         <v>13.826</v>
       </c>
-      <c r="F149">
-        <v>6</v>
+      <c r="F149" t="s">
+        <v>453</v>
       </c>
       <c r="H149">
         <v>25</v>
@@ -8409,8 +8433,8 @@
       <c r="D150">
         <v>13.826</v>
       </c>
-      <c r="F150">
-        <v>6</v>
+      <c r="F150" t="s">
+        <v>453</v>
       </c>
       <c r="H150">
         <v>25</v>
@@ -8465,8 +8489,8 @@
       <c r="D151">
         <v>13.826</v>
       </c>
-      <c r="F151">
-        <v>6</v>
+      <c r="F151" t="s">
+        <v>453</v>
       </c>
       <c r="H151">
         <v>25.65</v>
@@ -8521,8 +8545,8 @@
       <c r="D152">
         <v>13.826</v>
       </c>
-      <c r="F152">
-        <v>6</v>
+      <c r="F152" t="s">
+        <v>453</v>
       </c>
       <c r="H152">
         <v>25.5</v>
@@ -8574,8 +8598,8 @@
       <c r="D153">
         <v>10.5178</v>
       </c>
-      <c r="F153">
-        <v>6</v>
+      <c r="F153" t="s">
+        <v>453</v>
       </c>
       <c r="H153">
         <v>17.6</v>
@@ -8618,8 +8642,8 @@
       <c r="D154">
         <v>16.4728</v>
       </c>
-      <c r="F154">
-        <v>5</v>
+      <c r="F154" t="s">
+        <v>459</v>
       </c>
       <c r="H154">
         <v>24.3</v>
@@ -8674,8 +8698,8 @@
       <c r="D155">
         <v>16.6078</v>
       </c>
-      <c r="F155">
-        <v>5</v>
+      <c r="F155" t="s">
+        <v>459</v>
       </c>
       <c r="H155">
         <v>22.8</v>
@@ -8724,8 +8748,8 @@
       <c r="D156">
         <v>14.3315</v>
       </c>
-      <c r="F156">
-        <v>5</v>
+      <c r="F156" t="s">
+        <v>459</v>
       </c>
       <c r="H156">
         <v>8</v>
@@ -8750,8 +8774,8 @@
       <c r="D157">
         <v>14.256649</v>
       </c>
-      <c r="F157">
-        <v>5</v>
+      <c r="F157" t="s">
+        <v>459</v>
       </c>
       <c r="H157">
         <v>11.5</v>
@@ -8812,8 +8836,8 @@
       <c r="E158">
         <v>6</v>
       </c>
-      <c r="F158">
-        <v>5</v>
+      <c r="F158" t="s">
+        <v>459</v>
       </c>
       <c r="H158">
         <v>25.6</v>
@@ -8871,8 +8895,8 @@
       <c r="D159">
         <v>13.1518</v>
       </c>
-      <c r="F159">
-        <v>6</v>
+      <c r="F159" t="s">
+        <v>453</v>
       </c>
       <c r="H159">
         <v>11.5</v>
@@ -8918,8 +8942,8 @@
       <c r="D160">
         <v>13.4225</v>
       </c>
-      <c r="F160">
-        <v>5</v>
+      <c r="F160" t="s">
+        <v>459</v>
       </c>
       <c r="H160">
         <v>12.25</v>
@@ -8974,8 +8998,8 @@
       <c r="D161">
         <v>13.4225</v>
       </c>
-      <c r="F161">
-        <v>5</v>
+      <c r="F161" t="s">
+        <v>459</v>
       </c>
       <c r="H161">
         <v>11.3</v>
@@ -9030,8 +9054,8 @@
       <c r="D162">
         <v>11.1851</v>
       </c>
-      <c r="F162">
-        <v>6</v>
+      <c r="F162" t="s">
+        <v>453</v>
       </c>
       <c r="H162">
         <v>11.3</v>
@@ -9080,8 +9104,8 @@
       <c r="D163">
         <v>9.6715</v>
       </c>
-      <c r="F163">
-        <v>6</v>
+      <c r="F163" t="s">
+        <v>453</v>
       </c>
       <c r="H163">
         <v>15.6</v>
@@ -9124,8 +9148,8 @@
       <c r="D164">
         <v>10.242</v>
       </c>
-      <c r="F164">
-        <v>6</v>
+      <c r="F164" t="s">
+        <v>453</v>
       </c>
       <c r="H164">
         <v>8.800000000000001</v>
@@ -9165,8 +9189,8 @@
       <c r="D165">
         <v>9.7997</v>
       </c>
-      <c r="F165">
-        <v>8</v>
+      <c r="F165" t="s">
+        <v>455</v>
       </c>
       <c r="H165">
         <v>14.2</v>
@@ -9212,8 +9236,8 @@
       <c r="D166">
         <v>9.913399999999999</v>
       </c>
-      <c r="F166">
-        <v>5</v>
+      <c r="F166" t="s">
+        <v>459</v>
       </c>
       <c r="H166">
         <v>4.1</v>
@@ -9253,8 +9277,8 @@
       <c r="D167">
         <v>14.1295</v>
       </c>
-      <c r="F167">
-        <v>6</v>
+      <c r="F167" t="s">
+        <v>453</v>
       </c>
       <c r="H167">
         <v>7</v>
@@ -9306,8 +9330,8 @@
       <c r="D168">
         <v>14.5693</v>
       </c>
-      <c r="F168">
-        <v>8</v>
+      <c r="F168" t="s">
+        <v>455</v>
       </c>
       <c r="H168">
         <v>15.7</v>
@@ -9368,8 +9392,8 @@
       <c r="D169">
         <v>14.5693</v>
       </c>
-      <c r="F169">
-        <v>8</v>
+      <c r="F169" t="s">
+        <v>455</v>
       </c>
       <c r="H169">
         <v>14.7</v>
@@ -9427,8 +9451,8 @@
       <c r="D170">
         <v>14.8025</v>
       </c>
-      <c r="F170">
-        <v>8</v>
+      <c r="F170" t="s">
+        <v>455</v>
       </c>
       <c r="H170">
         <v>7.7</v>
@@ -9471,8 +9495,8 @@
       <c r="D171">
         <v>14.8025</v>
       </c>
-      <c r="F171">
-        <v>8</v>
+      <c r="F171" t="s">
+        <v>455</v>
       </c>
       <c r="H171">
         <v>9.9</v>
@@ -9524,8 +9548,8 @@
       <c r="D172">
         <v>10.9657</v>
       </c>
-      <c r="F172">
-        <v>8</v>
+      <c r="F172" t="s">
+        <v>455</v>
       </c>
       <c r="H172">
         <v>11.4</v>
@@ -9571,8 +9595,8 @@
       <c r="D173">
         <v>10.9657</v>
       </c>
-      <c r="F173">
-        <v>8</v>
+      <c r="F173" t="s">
+        <v>455</v>
       </c>
       <c r="H173">
         <v>7.4</v>
@@ -9615,8 +9639,8 @@
       <c r="D174">
         <v>14.5928</v>
       </c>
-      <c r="F174">
-        <v>8</v>
+      <c r="F174" t="s">
+        <v>455</v>
       </c>
       <c r="H174">
         <v>7.4</v>
@@ -9653,8 +9677,8 @@
       <c r="D175">
         <v>12.7669</v>
       </c>
-      <c r="F175">
-        <v>8</v>
+      <c r="F175" t="s">
+        <v>455</v>
       </c>
       <c r="H175">
         <v>12.3</v>
@@ -9697,8 +9721,8 @@
       <c r="D176">
         <v>13.1689</v>
       </c>
-      <c r="F176">
-        <v>8</v>
+      <c r="F176" t="s">
+        <v>455</v>
       </c>
       <c r="H176">
         <v>8.9</v>
@@ -9750,8 +9774,8 @@
       <c r="D177">
         <v>13.1689</v>
       </c>
-      <c r="F177">
-        <v>8</v>
+      <c r="F177" t="s">
+        <v>455</v>
       </c>
       <c r="H177">
         <v>5.3</v>
@@ -9803,8 +9827,8 @@
       <c r="D178">
         <v>13.5148</v>
       </c>
-      <c r="F178">
-        <v>8</v>
+      <c r="F178" t="s">
+        <v>455</v>
       </c>
       <c r="H178">
         <v>11.6</v>
@@ -9856,8 +9880,8 @@
       <c r="D179">
         <v>13.5028</v>
       </c>
-      <c r="F179">
-        <v>8</v>
+      <c r="F179" t="s">
+        <v>455</v>
       </c>
       <c r="H179">
         <v>11</v>
@@ -9900,8 +9924,8 @@
       <c r="D180">
         <v>10.6436</v>
       </c>
-      <c r="F180">
-        <v>8</v>
+      <c r="F180" t="s">
+        <v>455</v>
       </c>
       <c r="H180">
         <v>6.6</v>
@@ -9959,8 +9983,8 @@
       <c r="D181">
         <v>10.6626</v>
       </c>
-      <c r="F181">
-        <v>8</v>
+      <c r="F181" t="s">
+        <v>455</v>
       </c>
       <c r="H181">
         <v>9.6</v>
@@ -10015,8 +10039,8 @@
       <c r="D182">
         <v>9.979100000000001</v>
       </c>
-      <c r="F182">
-        <v>6</v>
+      <c r="F182" t="s">
+        <v>453</v>
       </c>
       <c r="H182">
         <v>11.9</v>
@@ -10059,8 +10083,8 @@
       <c r="D183">
         <v>9.9017</v>
       </c>
-      <c r="F183">
-        <v>6</v>
+      <c r="F183" t="s">
+        <v>453</v>
       </c>
       <c r="H183">
         <v>12.3</v>
@@ -10100,8 +10124,8 @@
       <c r="D184">
         <v>13.0571</v>
       </c>
-      <c r="F184">
-        <v>8</v>
+      <c r="F184" t="s">
+        <v>455</v>
       </c>
       <c r="H184">
         <v>10.9</v>
@@ -10141,8 +10165,8 @@
       <c r="D185">
         <v>15.32</v>
       </c>
-      <c r="F185">
-        <v>8</v>
+      <c r="F185" t="s">
+        <v>455</v>
       </c>
       <c r="H185">
         <v>10.8</v>
@@ -10203,8 +10227,8 @@
       <c r="E186">
         <v>8</v>
       </c>
-      <c r="F186">
-        <v>6</v>
+      <c r="F186" t="s">
+        <v>453</v>
       </c>
       <c r="H186">
         <v>24.3</v>
@@ -10265,8 +10289,8 @@
       <c r="E187">
         <v>53.1</v>
       </c>
-      <c r="F187">
-        <v>6</v>
+      <c r="F187" t="s">
+        <v>453</v>
       </c>
       <c r="H187">
         <v>22.5</v>
@@ -10321,8 +10345,8 @@
       <c r="E188">
         <v>8</v>
       </c>
-      <c r="F188">
-        <v>6</v>
+      <c r="F188" t="s">
+        <v>453</v>
       </c>
       <c r="H188">
         <v>21.3</v>
@@ -10383,8 +10407,8 @@
       <c r="E189">
         <v>7.75</v>
       </c>
-      <c r="F189">
-        <v>6</v>
+      <c r="F189" t="s">
+        <v>453</v>
       </c>
       <c r="H189">
         <v>24.5</v>
@@ -10445,8 +10469,8 @@
       <c r="E190">
         <v>12</v>
       </c>
-      <c r="F190">
-        <v>6</v>
+      <c r="F190" t="s">
+        <v>453</v>
       </c>
       <c r="H190">
         <v>20.3</v>
@@ -10504,8 +10528,8 @@
       <c r="E191">
         <v>15</v>
       </c>
-      <c r="F191">
-        <v>5</v>
+      <c r="F191" t="s">
+        <v>459</v>
       </c>
       <c r="H191">
         <v>11.8</v>
@@ -10530,8 +10554,8 @@
       <c r="D192">
         <v>14.986191</v>
       </c>
-      <c r="F192">
-        <v>6</v>
+      <c r="F192" t="s">
+        <v>453</v>
       </c>
       <c r="H192">
         <v>17.5</v>
@@ -10589,8 +10613,8 @@
       <c r="D193">
         <v>14.783171</v>
       </c>
-      <c r="F193">
-        <v>5</v>
+      <c r="F193" t="s">
+        <v>459</v>
       </c>
       <c r="H193">
         <v>24</v>
@@ -10648,8 +10672,8 @@
       <c r="D194">
         <v>13.629066</v>
       </c>
-      <c r="F194">
-        <v>6</v>
+      <c r="F194" t="s">
+        <v>453</v>
       </c>
       <c r="H194">
         <v>18.5</v>
@@ -10707,8 +10731,8 @@
       <c r="D195">
         <v>12.117442</v>
       </c>
-      <c r="F195">
-        <v>6</v>
+      <c r="F195" t="s">
+        <v>453</v>
       </c>
       <c r="H195">
         <v>14.5</v>
@@ -10769,8 +10793,8 @@
       <c r="D196">
         <v>13.782635</v>
       </c>
-      <c r="F196">
-        <v>6</v>
+      <c r="F196" t="s">
+        <v>453</v>
       </c>
       <c r="H196">
         <v>22.9</v>
@@ -10825,8 +10849,8 @@
       <c r="D197">
         <v>13.191587</v>
       </c>
-      <c r="F197">
-        <v>8</v>
+      <c r="F197" t="s">
+        <v>455</v>
       </c>
       <c r="H197">
         <v>15.2</v>
@@ -10881,8 +10905,8 @@
       <c r="E198">
         <v>5.2</v>
       </c>
-      <c r="F198">
-        <v>5</v>
+      <c r="F198" t="s">
+        <v>459</v>
       </c>
       <c r="H198">
         <v>14</v>
@@ -10949,8 +10973,8 @@
       <c r="E199">
         <v>6</v>
       </c>
-      <c r="F199">
-        <v>5</v>
+      <c r="F199" t="s">
+        <v>459</v>
       </c>
       <c r="H199">
         <v>19.6</v>
@@ -11005,8 +11029,8 @@
       <c r="E200">
         <v>22.5</v>
       </c>
-      <c r="F200">
-        <v>5</v>
+      <c r="F200" t="s">
+        <v>459</v>
       </c>
       <c r="H200">
         <v>14.2</v>
@@ -11070,8 +11094,8 @@
       <c r="E201">
         <v>85</v>
       </c>
-      <c r="F201">
-        <v>5</v>
+      <c r="F201" t="s">
+        <v>459</v>
       </c>
       <c r="H201">
         <v>13.9</v>
@@ -11129,8 +11153,8 @@
       <c r="E202">
         <v>86.42</v>
       </c>
-      <c r="F202">
-        <v>8</v>
+      <c r="F202" t="s">
+        <v>455</v>
       </c>
       <c r="H202">
         <v>12.95</v>
@@ -11191,8 +11215,8 @@
       <c r="E203">
         <v>100</v>
       </c>
-      <c r="F203">
-        <v>8</v>
+      <c r="F203" t="s">
+        <v>455</v>
       </c>
       <c r="H203">
         <v>12.6</v>
@@ -11256,8 +11280,8 @@
       <c r="E204">
         <v>30</v>
       </c>
-      <c r="F204">
-        <v>8</v>
+      <c r="F204" t="s">
+        <v>455</v>
       </c>
       <c r="H204">
         <v>13</v>
@@ -11321,8 +11345,8 @@
       <c r="D205">
         <v>14.802535</v>
       </c>
-      <c r="F205">
-        <v>8</v>
+      <c r="F205" t="s">
+        <v>455</v>
       </c>
       <c r="H205">
         <v>9.85</v>
@@ -11380,8 +11404,8 @@
       <c r="D206">
         <v>14.814508</v>
       </c>
-      <c r="F206">
-        <v>8</v>
+      <c r="F206" t="s">
+        <v>455</v>
       </c>
       <c r="H206">
         <v>10.3</v>
@@ -11439,8 +11463,8 @@
       <c r="D207">
         <v>14.777709</v>
       </c>
-      <c r="F207">
-        <v>8</v>
+      <c r="F207" t="s">
+        <v>455</v>
       </c>
       <c r="H207">
         <v>9.800000000000001</v>
@@ -11492,8 +11516,8 @@
       <c r="D208">
         <v>14.783736</v>
       </c>
-      <c r="F208">
-        <v>8</v>
+      <c r="F208" t="s">
+        <v>455</v>
       </c>
       <c r="H208">
         <v>9.9</v>
@@ -11548,8 +11572,8 @@
       <c r="D209">
         <v>14.760945</v>
       </c>
-      <c r="F209">
-        <v>8</v>
+      <c r="F209" t="s">
+        <v>455</v>
       </c>
       <c r="H209">
         <v>10.8</v>
@@ -11607,8 +11631,8 @@
       <c r="D210">
         <v>14.59296</v>
       </c>
-      <c r="F210">
-        <v>9</v>
+      <c r="F210" t="s">
+        <v>456</v>
       </c>
       <c r="H210">
         <v>10.1</v>
@@ -11666,8 +11690,8 @@
       <c r="D211">
         <v>14.59296</v>
       </c>
-      <c r="F211">
-        <v>9</v>
+      <c r="F211" t="s">
+        <v>456</v>
       </c>
       <c r="H211">
         <v>9.699999999999999</v>
@@ -11725,8 +11749,8 @@
       <c r="D212">
         <v>14.516993</v>
       </c>
-      <c r="F212">
-        <v>8</v>
+      <c r="F212" t="s">
+        <v>455</v>
       </c>
       <c r="H212">
         <v>7.5</v>
@@ -11781,8 +11805,8 @@
       <c r="D213">
         <v>14.5481</v>
       </c>
-      <c r="F213">
-        <v>6</v>
+      <c r="F213" t="s">
+        <v>453</v>
       </c>
       <c r="H213">
         <v>8.199999999999999</v>
@@ -11837,8 +11861,8 @@
       <c r="D214">
         <v>14.5481</v>
       </c>
-      <c r="F214">
-        <v>6</v>
+      <c r="F214" t="s">
+        <v>453</v>
       </c>
       <c r="H214">
         <v>8.6</v>
@@ -11893,8 +11917,8 @@
       <c r="D215">
         <v>14.536693</v>
       </c>
-      <c r="F215">
-        <v>6</v>
+      <c r="F215" t="s">
+        <v>453</v>
       </c>
       <c r="H215">
         <v>7.5</v>
@@ -11952,8 +11976,8 @@
       <c r="D216">
         <v>14.536693</v>
       </c>
-      <c r="F216">
-        <v>6</v>
+      <c r="F216" t="s">
+        <v>453</v>
       </c>
       <c r="H216">
         <v>7.3</v>
@@ -12014,8 +12038,8 @@
       <c r="D217">
         <v>14.557603</v>
       </c>
-      <c r="F217">
-        <v>6</v>
+      <c r="F217" t="s">
+        <v>453</v>
       </c>
       <c r="H217">
         <v>8.5</v>
@@ -12067,8 +12091,8 @@
       <c r="D218">
         <v>13.060723</v>
       </c>
-      <c r="F218">
-        <v>8</v>
+      <c r="F218" t="s">
+        <v>455</v>
       </c>
       <c r="H218">
         <v>10.2</v>
@@ -12120,8 +12144,8 @@
       <c r="D219">
         <v>13.194507</v>
       </c>
-      <c r="F219">
-        <v>6</v>
+      <c r="F219" t="s">
+        <v>453</v>
       </c>
       <c r="H219">
         <v>11.3</v>
@@ -12182,8 +12206,8 @@
       <c r="D220">
         <v>13.053921</v>
       </c>
-      <c r="F220">
-        <v>8</v>
+      <c r="F220" t="s">
+        <v>455</v>
       </c>
       <c r="H220">
         <v>9.300000000000001</v>
@@ -12244,8 +12268,8 @@
       <c r="D221">
         <v>13.035942</v>
       </c>
-      <c r="F221">
-        <v>6</v>
+      <c r="F221" t="s">
+        <v>453</v>
       </c>
       <c r="H221">
         <v>10.7</v>
@@ -12306,8 +12330,8 @@
       <c r="D222">
         <v>12.768106</v>
       </c>
-      <c r="F222">
-        <v>8</v>
+      <c r="F222" t="s">
+        <v>455</v>
       </c>
       <c r="H222">
         <v>12.5</v>
@@ -12368,8 +12392,8 @@
       <c r="D223">
         <v>12.766167</v>
       </c>
-      <c r="F223">
-        <v>8</v>
+      <c r="F223" t="s">
+        <v>455</v>
       </c>
       <c r="H223">
         <v>13.1</v>
@@ -12430,8 +12454,8 @@
       <c r="D224">
         <v>13.50178</v>
       </c>
-      <c r="F224">
-        <v>8</v>
+      <c r="F224" t="s">
+        <v>455</v>
       </c>
       <c r="H224">
         <v>16</v>
@@ -12486,8 +12510,8 @@
       <c r="D225">
         <v>13.495442</v>
       </c>
-      <c r="F225">
-        <v>8</v>
+      <c r="F225" t="s">
+        <v>455</v>
       </c>
       <c r="H225">
         <v>10.8</v>
@@ -12548,8 +12572,8 @@
       <c r="E226">
         <v>94</v>
       </c>
-      <c r="F226">
-        <v>6</v>
+      <c r="F226" t="s">
+        <v>453</v>
       </c>
       <c r="H226">
         <v>36.5</v>
@@ -12607,8 +12631,8 @@
       <c r="E227">
         <v>5</v>
       </c>
-      <c r="F227">
-        <v>6</v>
+      <c r="F227" t="s">
+        <v>453</v>
       </c>
       <c r="H227">
         <v>11.4</v>
@@ -12675,8 +12699,8 @@
       <c r="E228">
         <v>5</v>
       </c>
-      <c r="F228">
-        <v>6</v>
+      <c r="F228" t="s">
+        <v>453</v>
       </c>
       <c r="H228">
         <v>10.3</v>
@@ -12743,8 +12767,8 @@
       <c r="E229">
         <v>5</v>
       </c>
-      <c r="F229">
-        <v>6</v>
+      <c r="F229" t="s">
+        <v>453</v>
       </c>
       <c r="H229">
         <v>10.6</v>
@@ -12811,8 +12835,8 @@
       <c r="E230">
         <v>92</v>
       </c>
-      <c r="F230">
-        <v>8</v>
+      <c r="F230" t="s">
+        <v>455</v>
       </c>
       <c r="H230">
         <v>13.6</v>
@@ -12873,8 +12897,8 @@
       <c r="D231">
         <v>13.690503</v>
       </c>
-      <c r="F231">
-        <v>8</v>
+      <c r="F231" t="s">
+        <v>455</v>
       </c>
       <c r="H231">
         <v>9.800000000000001</v>
@@ -12926,8 +12950,8 @@
       <c r="D232">
         <v>12.507543</v>
       </c>
-      <c r="F232">
-        <v>8</v>
+      <c r="F232" t="s">
+        <v>455</v>
       </c>
       <c r="H232">
         <v>15</v>
@@ -12985,8 +13009,8 @@
       <c r="D233">
         <v>15.194748</v>
       </c>
-      <c r="F233">
-        <v>8</v>
+      <c r="F233" t="s">
+        <v>455</v>
       </c>
       <c r="H233">
         <v>13</v>
@@ -13041,8 +13065,8 @@
       <c r="E234">
         <v>9</v>
       </c>
-      <c r="F234">
-        <v>8</v>
+      <c r="F234" t="s">
+        <v>455</v>
       </c>
       <c r="H234">
         <v>10</v>
@@ -13106,8 +13130,8 @@
       <c r="E235">
         <v>7.2</v>
       </c>
-      <c r="F235">
-        <v>8</v>
+      <c r="F235" t="s">
+        <v>455</v>
       </c>
       <c r="H235">
         <v>13.5</v>
@@ -13165,8 +13189,8 @@
       <c r="D236">
         <v>15.312227</v>
       </c>
-      <c r="F236">
-        <v>8</v>
+      <c r="F236" t="s">
+        <v>455</v>
       </c>
       <c r="H236">
         <v>10</v>
@@ -13224,8 +13248,8 @@
       <c r="D237">
         <v>14.81086</v>
       </c>
-      <c r="F237">
-        <v>8</v>
+      <c r="F237" t="s">
+        <v>455</v>
       </c>
       <c r="H237">
         <v>10</v>
@@ -13286,8 +13310,8 @@
       <c r="D238">
         <v>14.163093</v>
       </c>
-      <c r="F238">
-        <v>8</v>
+      <c r="F238" t="s">
+        <v>455</v>
       </c>
       <c r="H238">
         <v>8</v>
@@ -13345,8 +13369,8 @@
       <c r="D239">
         <v>14.151461</v>
       </c>
-      <c r="F239">
-        <v>5</v>
+      <c r="F239" t="s">
+        <v>459</v>
       </c>
       <c r="H239">
         <v>6.9</v>
@@ -13404,8 +13428,8 @@
       <c r="D240">
         <v>14.151461</v>
       </c>
-      <c r="F240">
-        <v>5</v>
+      <c r="F240" t="s">
+        <v>459</v>
       </c>
       <c r="H240">
         <v>9.5</v>
@@ -13463,8 +13487,8 @@
       <c r="D241">
         <v>14.151461</v>
       </c>
-      <c r="F241">
-        <v>5</v>
+      <c r="F241" t="s">
+        <v>459</v>
       </c>
       <c r="H241">
         <v>9.800000000000001</v>
@@ -13525,8 +13549,8 @@
       <c r="D242">
         <v>14.151461</v>
       </c>
-      <c r="F242">
-        <v>5</v>
+      <c r="F242" t="s">
+        <v>459</v>
       </c>
       <c r="H242">
         <v>8.699999999999999</v>
@@ -13584,8 +13608,8 @@
       <c r="D243">
         <v>14.151461</v>
       </c>
-      <c r="F243">
-        <v>5</v>
+      <c r="F243" t="s">
+        <v>459</v>
       </c>
       <c r="H243">
         <v>8.699999999999999</v>
@@ -13643,8 +13667,8 @@
       <c r="D244">
         <v>14.151461</v>
       </c>
-      <c r="F244">
-        <v>5</v>
+      <c r="F244" t="s">
+        <v>459</v>
       </c>
       <c r="H244">
         <v>8.6</v>
@@ -13702,8 +13726,8 @@
       <c r="D245">
         <v>11.863071</v>
       </c>
-      <c r="F245">
-        <v>6</v>
+      <c r="F245" t="s">
+        <v>453</v>
       </c>
       <c r="H245">
         <v>9.800000000000001</v>
@@ -13767,8 +13791,8 @@
       <c r="D246">
         <v>6.217712402</v>
       </c>
-      <c r="F246">
-        <v>6</v>
+      <c r="F246" t="s">
+        <v>453</v>
       </c>
       <c r="H246">
         <v>30</v>
@@ -13793,8 +13817,8 @@
       <c r="D247">
         <v>6.550720215</v>
       </c>
-      <c r="F247">
-        <v>6</v>
+      <c r="F247" t="s">
+        <v>453</v>
       </c>
       <c r="H247">
         <v>34.25</v>
@@ -13819,8 +13843,8 @@
       <c r="D248">
         <v>6.463928223</v>
       </c>
-      <c r="F248">
-        <v>3</v>
+      <c r="F248" t="s">
+        <v>454</v>
       </c>
       <c r="H248">
         <v>30</v>
@@ -13845,8 +13869,8 @@
       <c r="D249">
         <v>6.550476074</v>
       </c>
-      <c r="F249">
-        <v>3</v>
+      <c r="F249" t="s">
+        <v>454</v>
       </c>
       <c r="H249">
         <v>37.5</v>
@@ -13871,8 +13895,8 @@
       <c r="D250">
         <v>5.782287598</v>
       </c>
-      <c r="F250">
-        <v>6</v>
+      <c r="F250" t="s">
+        <v>453</v>
       </c>
       <c r="H250">
         <v>58.5</v>
@@ -13897,8 +13921,8 @@
       <c r="D251">
         <v>6.76171875</v>
       </c>
-      <c r="F251">
-        <v>6</v>
+      <c r="F251" t="s">
+        <v>453</v>
       </c>
       <c r="H251">
         <v>32</v>
@@ -13923,8 +13947,8 @@
       <c r="D252">
         <v>5.833496094</v>
       </c>
-      <c r="F252">
-        <v>6</v>
+      <c r="F252" t="s">
+        <v>453</v>
       </c>
       <c r="H252">
         <v>34</v>
@@ -13949,8 +13973,8 @@
       <c r="D253">
         <v>6.067687987999999</v>
       </c>
-      <c r="F253">
-        <v>6</v>
+      <c r="F253" t="s">
+        <v>453</v>
       </c>
       <c r="H253">
         <v>19.5</v>
@@ -13975,8 +13999,8 @@
       <c r="D254">
         <v>7.361083983999999</v>
       </c>
-      <c r="F254">
-        <v>5</v>
+      <c r="F254" t="s">
+        <v>459</v>
       </c>
       <c r="H254">
         <v>30</v>
@@ -14001,8 +14025,8 @@
       <c r="D255">
         <v>5.985107422</v>
       </c>
-      <c r="F255">
-        <v>6</v>
+      <c r="F255" t="s">
+        <v>453</v>
       </c>
       <c r="H255">
         <v>37</v>
@@ -14030,8 +14054,8 @@
       <c r="E256">
         <v>7.45</v>
       </c>
-      <c r="F256">
-        <v>6</v>
+      <c r="F256" t="s">
+        <v>453</v>
       </c>
       <c r="H256">
         <v>39.6</v>
@@ -14089,8 +14113,8 @@
       <c r="D257">
         <v>6.70595</v>
       </c>
-      <c r="F257">
-        <v>6</v>
+      <c r="F257" t="s">
+        <v>453</v>
       </c>
       <c r="H257">
         <v>32.8</v>
@@ -14148,8 +14172,8 @@
       <c r="D258">
         <v>6.70595</v>
       </c>
-      <c r="F258">
-        <v>6</v>
+      <c r="F258" t="s">
+        <v>453</v>
       </c>
       <c r="H258">
         <v>33.6</v>
@@ -14201,8 +14225,8 @@
       <c r="D259">
         <v>6.70611111</v>
       </c>
-      <c r="F259">
-        <v>6</v>
+      <c r="F259" t="s">
+        <v>453</v>
       </c>
       <c r="H259">
         <v>25</v>
@@ -14257,8 +14281,8 @@
       <c r="D260">
         <v>5.44527778</v>
       </c>
-      <c r="F260">
-        <v>5</v>
+      <c r="F260" t="s">
+        <v>459</v>
       </c>
       <c r="H260">
         <v>35.5</v>
@@ -14283,8 +14307,8 @@
       <c r="D261">
         <v>5.44527778</v>
       </c>
-      <c r="F261">
-        <v>5</v>
+      <c r="F261" t="s">
+        <v>459</v>
       </c>
       <c r="H261">
         <v>19</v>
@@ -14309,8 +14333,8 @@
       <c r="D262">
         <v>6.084013</v>
       </c>
-      <c r="F262">
-        <v>8</v>
+      <c r="F262" t="s">
+        <v>455</v>
       </c>
       <c r="H262">
         <v>16.7</v>
@@ -14365,8 +14389,8 @@
       <c r="D263">
         <v>6.54715688</v>
       </c>
-      <c r="F263">
-        <v>3</v>
+      <c r="F263" t="s">
+        <v>454</v>
       </c>
       <c r="H263">
         <v>8</v>
@@ -14421,8 +14445,8 @@
       <c r="D264">
         <v>6.54715688</v>
       </c>
-      <c r="F264">
-        <v>3</v>
+      <c r="F264" t="s">
+        <v>454</v>
       </c>
       <c r="H264">
         <v>13</v>
@@ -14462,8 +14486,8 @@
       <c r="D265">
         <v>7.30982505</v>
       </c>
-      <c r="F265">
-        <v>8</v>
+      <c r="F265" t="s">
+        <v>455</v>
       </c>
       <c r="H265">
         <v>28.95</v>
@@ -14509,8 +14533,8 @@
       <c r="D266">
         <v>7.309825</v>
       </c>
-      <c r="F266">
-        <v>8</v>
+      <c r="F266" t="s">
+        <v>455</v>
       </c>
       <c r="H266">
         <v>22.95</v>
@@ -14556,8 +14580,8 @@
       <c r="D267">
         <v>6.570693449</v>
       </c>
-      <c r="F267">
-        <v>3</v>
+      <c r="F267" t="s">
+        <v>454</v>
       </c>
       <c r="H267">
         <v>35.2</v>
@@ -14585,8 +14609,8 @@
       <c r="E268">
         <v>4.5</v>
       </c>
-      <c r="F268">
-        <v>3</v>
+      <c r="F268" t="s">
+        <v>454</v>
       </c>
       <c r="H268">
         <v>38</v>
@@ -14641,8 +14665,8 @@
       <c r="D269">
         <v>5.988171864</v>
       </c>
-      <c r="F269">
-        <v>6</v>
+      <c r="F269" t="s">
+        <v>453</v>
       </c>
       <c r="H269">
         <v>9.5</v>
@@ -14697,8 +14721,8 @@
       <c r="D270">
         <v>6.878868607</v>
       </c>
-      <c r="F270">
-        <v>6</v>
+      <c r="F270" t="s">
+        <v>453</v>
       </c>
       <c r="H270">
         <v>7.5</v>
@@ -14726,8 +14750,8 @@
       <c r="E271">
         <v>17.1</v>
       </c>
-      <c r="F271">
-        <v>6</v>
+      <c r="F271" t="s">
+        <v>453</v>
       </c>
       <c r="H271">
         <v>10.8</v>
@@ -14761,8 +14785,8 @@
       <c r="E272">
         <v>13.5</v>
       </c>
-      <c r="F272">
-        <v>6</v>
+      <c r="F272" t="s">
+        <v>453</v>
       </c>
       <c r="H272">
         <v>10.2</v>
@@ -14814,8 +14838,8 @@
       <c r="D273">
         <v>6.24789036</v>
       </c>
-      <c r="F273">
-        <v>6</v>
+      <c r="F273" t="s">
+        <v>453</v>
       </c>
       <c r="H273">
         <v>25.2</v>
@@ -14837,8 +14861,8 @@
       <c r="D274">
         <v>6.706080394</v>
       </c>
-      <c r="F274">
-        <v>6</v>
+      <c r="F274" t="s">
+        <v>453</v>
       </c>
       <c r="H274">
         <v>41</v>
@@ -14887,8 +14911,8 @@
       <c r="D275">
         <v>6.359454212</v>
       </c>
-      <c r="F275">
-        <v>6</v>
+      <c r="F275" t="s">
+        <v>453</v>
       </c>
       <c r="H275">
         <v>40</v>
@@ -14937,8 +14961,8 @@
       <c r="E276">
         <v>14</v>
       </c>
-      <c r="F276">
-        <v>6</v>
+      <c r="F276" t="s">
+        <v>453</v>
       </c>
       <c r="H276">
         <v>54</v>
@@ -14966,8 +14990,8 @@
       <c r="E277">
         <v>18.2</v>
       </c>
-      <c r="F277">
-        <v>6</v>
+      <c r="F277" t="s">
+        <v>453</v>
       </c>
       <c r="H277">
         <v>51</v>
@@ -15025,8 +15049,8 @@
       <c r="E278">
         <v>16</v>
       </c>
-      <c r="F278">
-        <v>6</v>
+      <c r="F278" t="s">
+        <v>453</v>
       </c>
       <c r="H278">
         <v>51</v>
@@ -15084,8 +15108,8 @@
       <c r="E279">
         <v>12</v>
       </c>
-      <c r="F279">
-        <v>6</v>
+      <c r="F279" t="s">
+        <v>453</v>
       </c>
       <c r="H279">
         <v>51</v>
@@ -15140,8 +15164,8 @@
       <c r="E280">
         <v>23.95</v>
       </c>
-      <c r="F280">
-        <v>6</v>
+      <c r="F280" t="s">
+        <v>453</v>
       </c>
       <c r="H280">
         <v>49.5</v>
@@ -15199,8 +15223,8 @@
       <c r="E281">
         <v>75</v>
       </c>
-      <c r="F281">
-        <v>5</v>
+      <c r="F281" t="s">
+        <v>459</v>
       </c>
       <c r="H281">
         <v>11.8</v>
@@ -15261,8 +15285,8 @@
       <c r="D282">
         <v>5.44605686</v>
       </c>
-      <c r="F282">
-        <v>6</v>
+      <c r="F282" t="s">
+        <v>453</v>
       </c>
       <c r="H282">
         <v>11.4</v>
@@ -15323,8 +15347,8 @@
       <c r="D283">
         <v>5.455578599999999</v>
       </c>
-      <c r="F283">
-        <v>5</v>
+      <c r="F283" t="s">
+        <v>459</v>
       </c>
       <c r="H283">
         <v>14.6</v>
@@ -15382,8 +15406,8 @@
       <c r="D284">
         <v>5.63828</v>
       </c>
-      <c r="F284">
-        <v>3</v>
+      <c r="F284" t="s">
+        <v>454</v>
       </c>
       <c r="H284">
         <v>58</v>
@@ -15411,8 +15435,8 @@
       <c r="E285">
         <v>7.5</v>
       </c>
-      <c r="F285">
-        <v>6</v>
+      <c r="F285" t="s">
+        <v>453</v>
       </c>
       <c r="H285">
         <v>13</v>
@@ -15437,8 +15461,8 @@
       <c r="D286">
         <v>5.00687996</v>
       </c>
-      <c r="F286">
-        <v>5</v>
+      <c r="F286" t="s">
+        <v>459</v>
       </c>
       <c r="H286">
         <v>25</v>
@@ -15463,8 +15487,8 @@
       <c r="D287">
         <v>6.52881821</v>
       </c>
-      <c r="F287">
-        <v>6</v>
+      <c r="F287" t="s">
+        <v>453</v>
       </c>
       <c r="H287">
         <v>32</v>
@@ -15519,8 +15543,8 @@
       <c r="D288">
         <v>6.52869257</v>
       </c>
-      <c r="F288">
-        <v>6</v>
+      <c r="F288" t="s">
+        <v>453</v>
       </c>
       <c r="H288">
         <v>34</v>
@@ -15575,8 +15599,8 @@
       <c r="D289">
         <v>6.528151253</v>
       </c>
-      <c r="F289">
-        <v>6</v>
+      <c r="F289" t="s">
+        <v>453</v>
       </c>
       <c r="H289">
         <v>33.7</v>
@@ -15604,8 +15628,8 @@
       <c r="E290">
         <v>8</v>
       </c>
-      <c r="F290">
-        <v>3</v>
+      <c r="F290" t="s">
+        <v>454</v>
       </c>
       <c r="H290">
         <v>27</v>
@@ -15663,8 +15687,8 @@
       <c r="D291">
         <v>6.683427</v>
       </c>
-      <c r="F291">
-        <v>6</v>
+      <c r="F291" t="s">
+        <v>453</v>
       </c>
       <c r="H291">
         <v>41.4</v>
@@ -15713,8 +15737,8 @@
       <c r="D292">
         <v>15.2372</v>
       </c>
-      <c r="F292">
-        <v>1</v>
+      <c r="F292" t="s">
+        <v>452</v>
       </c>
       <c r="H292">
         <v>35.3</v>
@@ -15757,8 +15781,8 @@
       <c r="D293">
         <v>15.2283</v>
       </c>
-      <c r="F293">
-        <v>5</v>
+      <c r="F293" t="s">
+        <v>459</v>
       </c>
       <c r="H293">
         <v>35</v>
@@ -15804,8 +15828,8 @@
       <c r="D294">
         <v>14.262091</v>
       </c>
-      <c r="F294">
-        <v>5</v>
+      <c r="F294" t="s">
+        <v>459</v>
       </c>
       <c r="H294">
         <v>19.5</v>
@@ -15848,8 +15872,8 @@
       <c r="D295">
         <v>14.187038</v>
       </c>
-      <c r="F295">
-        <v>7</v>
+      <c r="F295" t="s">
+        <v>454</v>
       </c>
       <c r="H295">
         <v>15.15</v>
@@ -15898,8 +15922,8 @@
       <c r="D296">
         <v>15.0219</v>
       </c>
-      <c r="F296">
-        <v>1</v>
+      <c r="F296" t="s">
+        <v>452</v>
       </c>
       <c r="H296">
         <v>29.5</v>
@@ -15948,8 +15972,8 @@
       <c r="D297">
         <v>14.8715</v>
       </c>
-      <c r="F297">
-        <v>6</v>
+      <c r="F297" t="s">
+        <v>453</v>
       </c>
       <c r="H297">
         <v>15</v>
@@ -16007,8 +16031,8 @@
       <c r="D298">
         <v>14.1891</v>
       </c>
-      <c r="F298">
-        <v>6</v>
+      <c r="F298" t="s">
+        <v>453</v>
       </c>
       <c r="H298">
         <v>13.5</v>
@@ -16063,8 +16087,8 @@
       <c r="D299">
         <v>14.1524</v>
       </c>
-      <c r="F299">
-        <v>1</v>
+      <c r="F299" t="s">
+        <v>452</v>
       </c>
       <c r="H299">
         <v>24.4</v>
@@ -16122,8 +16146,8 @@
       <c r="D300">
         <v>14.9986</v>
       </c>
-      <c r="F300">
-        <v>6</v>
+      <c r="F300" t="s">
+        <v>453</v>
       </c>
       <c r="H300">
         <v>27</v>
@@ -16166,8 +16190,8 @@
       <c r="D301">
         <v>14.9328</v>
       </c>
-      <c r="F301">
-        <v>6</v>
+      <c r="F301" t="s">
+        <v>453</v>
       </c>
       <c r="H301">
         <v>25.5</v>
@@ -16216,8 +16240,8 @@
       <c r="E302">
         <v>78</v>
       </c>
-      <c r="F302">
-        <v>6</v>
+      <c r="F302" t="s">
+        <v>453</v>
       </c>
       <c r="H302">
         <v>32</v>
@@ -16263,8 +16287,8 @@
       <c r="D303">
         <v>13.8937</v>
       </c>
-      <c r="F303">
-        <v>6</v>
+      <c r="F303" t="s">
+        <v>453</v>
       </c>
       <c r="H303">
         <v>5.9</v>
@@ -16307,8 +16331,8 @@
       <c r="D304">
         <v>13.9845</v>
       </c>
-      <c r="F304">
-        <v>6</v>
+      <c r="F304" t="s">
+        <v>453</v>
       </c>
       <c r="H304">
         <v>5.95</v>
@@ -16351,8 +16375,8 @@
       <c r="D305">
         <v>14.0392</v>
       </c>
-      <c r="F305">
-        <v>6</v>
+      <c r="F305" t="s">
+        <v>453</v>
       </c>
       <c r="H305">
         <v>6.7</v>
@@ -16395,8 +16419,8 @@
       <c r="D306">
         <v>14.0604</v>
       </c>
-      <c r="F306">
-        <v>6</v>
+      <c r="F306" t="s">
+        <v>453</v>
       </c>
       <c r="H306">
         <v>7.6</v>
@@ -16439,8 +16463,8 @@
       <c r="D307">
         <v>14.2822</v>
       </c>
-      <c r="F307">
-        <v>6</v>
+      <c r="F307" t="s">
+        <v>453</v>
       </c>
       <c r="H307">
         <v>7.050000000000002</v>
@@ -16483,8 +16507,8 @@
       <c r="D308">
         <v>14.5992</v>
       </c>
-      <c r="F308">
-        <v>5</v>
+      <c r="F308" t="s">
+        <v>459</v>
       </c>
       <c r="H308">
         <v>7.4</v>
@@ -16524,8 +16548,8 @@
       <c r="D309">
         <v>14.6456</v>
       </c>
-      <c r="F309">
-        <v>6</v>
+      <c r="F309" t="s">
+        <v>453</v>
       </c>
       <c r="H309">
         <v>7.4</v>
@@ -16568,8 +16592,8 @@
       <c r="D310">
         <v>14.7128</v>
       </c>
-      <c r="F310">
-        <v>6</v>
+      <c r="F310" t="s">
+        <v>453</v>
       </c>
       <c r="H310">
         <v>7.9</v>
@@ -16612,8 +16636,8 @@
       <c r="D311">
         <v>14.6061</v>
       </c>
-      <c r="F311">
-        <v>1</v>
+      <c r="F311" t="s">
+        <v>452</v>
       </c>
       <c r="H311">
         <v>5.5</v>
@@ -16659,8 +16683,8 @@
       <c r="D312">
         <v>11.74108887</v>
       </c>
-      <c r="F312">
-        <v>1</v>
+      <c r="F312" t="s">
+        <v>452</v>
       </c>
       <c r="H312">
         <v>19.05</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/ALPS_Datenbank/after_conversion_alps_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/ALPS_Datenbank/after_conversion_alps_mapped_readable.xlsx
@@ -1387,7 +1387,7 @@
     <t>Basalt</t>
   </si>
   <si>
-    <t>Syenite</t>
+    <t>Salt</t>
   </si>
   <si>
     <t>Breccia</t>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/ALPS_Datenbank/after_conversion_alps_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/ALPS_Datenbank/after_conversion_alps_mapped_readable.xlsx
@@ -16692,6 +16692,9 @@
       <c r="L312">
         <v>0</v>
       </c>
+      <c r="AD312">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
